--- a/SeaAroundUsExtraction/global_output/regional_calculations/HS_081_Pacific_Southwest.xlsx
+++ b/SeaAroundUsExtraction/global_output/regional_calculations/HS_081_Pacific_Southwest.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R4511290e4d0b4941"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rdb73ab86cff34f41"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rb7bbd8a6254845c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R0e9e27313dab442b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R5e321fc2b868459d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R1bb5938f1a4c4718"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R4b47eba8e3424b48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R6650d62869da4991"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rb47f4c88e03f46c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R27de0de7c6f04092"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rd91cd55e8c7d4fd6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rffac25f7632148d9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.0"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -83,99 +81,8 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="22">
+  <x:borders count="11">
     <x:border/>
-    <x:border/>
-    <x:border>
-      <x:right style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:right>
-      <x:bottom style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:right>
-      <x:bottom style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:left>
-      <x:bottom style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:right style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:left>
-      <x:top style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:right style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:top>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:top>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:left>
-      <x:top style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:top>
-    </x:border>
     <x:border>
       <x:right style="thin">
         <x:color rgb="FFD0D5DD"/>
@@ -271,46 +178,36 @@
         <x:color rgb="FF147D92"/>
       </x:bottom>
     </x:border>
-    <x:border>
-      <x:bottom style="medium">
-        <x:color rgb="FF147D92"/>
-      </x:bottom>
-    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="69">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
@@ -326,77 +223,40 @@
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="201" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="202" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -407,30 +267,25 @@
         </x:patternFill>
       </x:fill>
     </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
   </x:dxfs>
 </x:styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<xfpb:FeaturePropertyBags xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <xfpb:bag type="Checkbox"/>
+  <xfpb:bag type="XFControls">
+    <xfpb:bagId k="CellControl">0</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplement">
+    <xfpb:bagId k="XFControls">1</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <xfpb:a k="MappedFeaturePropertyBags">
+      <xfpb:bagId>2</xfpb:bagId>
+    </xfpb:a>
+  </xfpb:bag>
+</xfpb:FeaturePropertyBags>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -464,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="HS081CommercialTable" displayName="HS081CommercialTable" ref="A1:O5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O5"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="HS081CommercialTable" displayName="HS081CommercialTable" ref="A1:E5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E5"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="HS081FunctionalTable" displayName="HS081FunctionalTable" ref="A1:O5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O5"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="HS081FunctionalTable" displayName="HS081FunctionalTable" ref="A1:E5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E5"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="HS081ValidationTable" displayName="HS081ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="HS081ValidationTable" displayName="HS081ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -743,1875 +578,1875 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="56" t="str">
+      <x:c r="A1" s="29" t="str">
         <x:v>unit_id</x:v>
       </x:c>
-      <x:c r="B1" s="56" t="str">
+      <x:c r="B1" s="29" t="str">
         <x:v>region_name</x:v>
       </x:c>
-      <x:c r="C1" s="56" t="str">
+      <x:c r="C1" s="29" t="str">
         <x:v>region_type</x:v>
       </x:c>
-      <x:c r="D1" s="56" t="str">
+      <x:c r="D1" s="29" t="str">
         <x:v>year</x:v>
       </x:c>
-      <x:c r="E1" s="56" t="str">
+      <x:c r="E1" s="29" t="str">
         <x:v>taxon</x:v>
       </x:c>
-      <x:c r="F1" s="56" t="str">
+      <x:c r="F1" s="29" t="str">
         <x:v>common_name</x:v>
       </x:c>
-      <x:c r="G1" s="56" t="str">
+      <x:c r="G1" s="29" t="str">
         <x:v>functional_group</x:v>
       </x:c>
-      <x:c r="H1" s="56" t="str">
+      <x:c r="H1" s="29" t="str">
         <x:v>commercial_group</x:v>
       </x:c>
-      <x:c r="I1" s="56" t="str">
+      <x:c r="I1" s="29" t="str">
         <x:v>catch_tonnes</x:v>
       </x:c>
-      <x:c r="J1" s="56" t="str">
+      <x:c r="J1" s="29" t="str">
         <x:v>landings_tonnes</x:v>
       </x:c>
-      <x:c r="K1" s="56" t="str">
+      <x:c r="K1" s="29" t="str">
         <x:v>discards_tonnes</x:v>
       </x:c>
-      <x:c r="L1" s="56" t="str">
+      <x:c r="L1" s="29" t="str">
         <x:v>reported_tonnes</x:v>
       </x:c>
-      <x:c r="M1" s="56" t="str">
+      <x:c r="M1" s="29" t="str">
         <x:v>unreported_tonnes</x:v>
       </x:c>
-      <x:c r="N1" s="56" t="str">
+      <x:c r="N1" s="29" t="str">
         <x:v>taxon_key</x:v>
       </x:c>
-      <x:c r="O1" s="56" t="str">
+      <x:c r="O1" s="29" t="str">
         <x:v>tl</x:v>
       </x:c>
-      <x:c r="P1" s="56" t="str">
+      <x:c r="P1" s="29" t="str">
         <x:v>match_method</x:v>
       </x:c>
-      <x:c r="Q1" s="56" t="str">
+      <x:c r="Q1" s="29" t="str">
         <x:v>tl_source</x:v>
       </x:c>
-      <x:c r="R1" s="56" t="str">
+      <x:c r="R1" s="29" t="str">
         <x:v>match_confidence</x:v>
       </x:c>
-      <x:c r="S1" s="56" t="str">
+      <x:c r="S1" s="29" t="str">
         <x:v>reference_taxon</x:v>
       </x:c>
-      <x:c r="T1" s="56" t="str">
+      <x:c r="T1" s="29" t="str">
         <x:v>sppr</x:v>
       </x:c>
-      <x:c r="U1" s="56" t="str">
+      <x:c r="U1" s="29" t="str">
         <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
-      <x:c r="A2" s="46" t="str">
-        <x:v>HS_081</x:v>
-      </x:c>
-      <x:c r="B2" s="46" t="str">
+      <x:c r="A2" s="24" t="str">
+        <x:v>HS_081</x:v>
+      </x:c>
+      <x:c r="B2" s="24" t="str">
         <x:v>Pacific, Southwest</x:v>
       </x:c>
-      <x:c r="C2" s="46" t="str">
+      <x:c r="C2" s="24" t="str">
         <x:v>High Seas</x:v>
       </x:c>
-      <x:c r="D2" s="58" t="n">
+      <x:c r="D2" s="30" t="n">
         <x:v>2019</x:v>
       </x:c>
-      <x:c r="E2" s="46" t="str">
+      <x:c r="E2" s="24" t="str">
         <x:v>Thunnus alalunga</x:v>
       </x:c>
-      <x:c r="F2" s="46" t="str">
+      <x:c r="F2" s="24" t="str">
         <x:v>Albacore</x:v>
       </x:c>
-      <x:c r="G2" s="46" t="str">
+      <x:c r="G2" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="H2" s="46" t="str">
+      <x:c r="H2" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="I2" s="60" t="n">
+      <x:c r="I2" s="31" t="n">
         <x:v>17846.0256526858</x:v>
       </x:c>
-      <x:c r="J2" s="60" t="n">
+      <x:c r="J2" s="31" t="n">
         <x:v>17845.897325373102</x:v>
       </x:c>
-      <x:c r="K2" s="60" t="n">
+      <x:c r="K2" s="31" t="n">
         <x:v>0.1283273127</x:v>
       </x:c>
-      <x:c r="L2" s="60" t="n">
+      <x:c r="L2" s="31" t="n">
         <x:v>17845.897325373102</x:v>
       </x:c>
-      <x:c r="M2" s="60" t="n">
+      <x:c r="M2" s="31" t="n">
         <x:v>0.1283273127</x:v>
       </x:c>
-      <x:c r="N2" s="46" t="str">
+      <x:c r="N2" s="24" t="str">
         <x:v>thunnus alalunga</x:v>
       </x:c>
-      <x:c r="O2" s="62" t="n">
+      <x:c r="O2" s="32" t="n">
         <x:v>4.3</x:v>
       </x:c>
-      <x:c r="P2" s="46" t="str">
+      <x:c r="P2" s="24" t="str">
         <x:v>exact_2020_supplement</x:v>
       </x:c>
-      <x:c r="Q2" s="62" t="str">
+      <x:c r="Q2" s="32" t="str">
         <x:v>2020 supplement MeanTL</x:v>
       </x:c>
-      <x:c r="R2" s="46" t="str">
+      <x:c r="R2" s="24" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="S2" s="46" t="str">
+      <x:c r="S2" s="24" t="str">
         <x:v>Thunnus alalunga</x:v>
       </x:c>
-      <x:c r="T2" s="62" t="n">
+      <x:c r="T2" s="32" t="n">
         <x:f>IF(O2="","",(1/'Metadata'!$B$5)^(O2-1))</x:f>
         <x:v>1995.2623149688789</x:v>
       </x:c>
-      <x:c r="U2" s="60" t="n">
+      <x:c r="U2" s="31" t="n">
         <x:f>IF(T2="","",I2*T2)</x:f>
         <x:v>35607502.456771865</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
-      <x:c r="A3" s="46" t="str">
-        <x:v>HS_081</x:v>
-      </x:c>
-      <x:c r="B3" s="46" t="str">
+      <x:c r="A3" s="24" t="str">
+        <x:v>HS_081</x:v>
+      </x:c>
+      <x:c r="B3" s="24" t="str">
         <x:v>Pacific, Southwest</x:v>
       </x:c>
-      <x:c r="C3" s="46" t="str">
+      <x:c r="C3" s="24" t="str">
         <x:v>High Seas</x:v>
       </x:c>
-      <x:c r="D3" s="58" t="n">
+      <x:c r="D3" s="30" t="n">
         <x:v>2019</x:v>
       </x:c>
-      <x:c r="E3" s="46" t="str">
+      <x:c r="E3" s="24" t="str">
         <x:v>Prionace glauca</x:v>
       </x:c>
-      <x:c r="F3" s="46" t="str">
+      <x:c r="F3" s="24" t="str">
         <x:v>Blue shark</x:v>
       </x:c>
-      <x:c r="G3" s="46" t="str">
+      <x:c r="G3" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="H3" s="46" t="str">
+      <x:c r="H3" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="I3" s="60" t="n">
+      <x:c r="I3" s="31" t="n">
         <x:v>10354.8489961172</x:v>
       </x:c>
-      <x:c r="J3" s="60" t="n">
+      <x:c r="J3" s="31" t="n">
         <x:v>4867.90735761</x:v>
       </x:c>
-      <x:c r="K3" s="60" t="n">
+      <x:c r="K3" s="31" t="n">
         <x:v>5486.9416385072</x:v>
       </x:c>
-      <x:c r="L3" s="60" t="n">
+      <x:c r="L3" s="31" t="n">
         <x:v>4867.90735761</x:v>
       </x:c>
-      <x:c r="M3" s="60" t="n">
+      <x:c r="M3" s="31" t="n">
         <x:v>5486.9416385072</x:v>
       </x:c>
-      <x:c r="N3" s="46" t="str">
+      <x:c r="N3" s="24" t="str">
         <x:v>prionace glauca</x:v>
       </x:c>
-      <x:c r="O3" s="62" t="n">
+      <x:c r="O3" s="32" t="n">
         <x:v>4.35</x:v>
       </x:c>
-      <x:c r="P3" s="46" t="str">
+      <x:c r="P3" s="24" t="str">
         <x:v>exact_2020_supplement</x:v>
       </x:c>
-      <x:c r="Q3" s="62" t="str">
+      <x:c r="Q3" s="32" t="str">
         <x:v>2020 supplement MeanTL</x:v>
       </x:c>
-      <x:c r="R3" s="46" t="str">
+      <x:c r="R3" s="24" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="S3" s="46" t="str">
+      <x:c r="S3" s="24" t="str">
         <x:v>Prionace glauca</x:v>
       </x:c>
-      <x:c r="T3" s="62" t="n">
+      <x:c r="T3" s="32" t="n">
         <x:f>IF(O3="","",(1/'Metadata'!$B$5)^(O3-1))</x:f>
         <x:v>2238.7211385683377</x:v>
       </x:c>
-      <x:c r="U3" s="60" t="n">
+      <x:c r="U3" s="31" t="n">
         <x:f>IF(T3="","",I3*T3)</x:f>
         <x:v>23181619.334290706</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
-      <x:c r="A4" s="46" t="str">
-        <x:v>HS_081</x:v>
-      </x:c>
-      <x:c r="B4" s="46" t="str">
+      <x:c r="A4" s="24" t="str">
+        <x:v>HS_081</x:v>
+      </x:c>
+      <x:c r="B4" s="24" t="str">
         <x:v>Pacific, Southwest</x:v>
       </x:c>
-      <x:c r="C4" s="46" t="str">
+      <x:c r="C4" s="24" t="str">
         <x:v>High Seas</x:v>
       </x:c>
-      <x:c r="D4" s="58" t="n">
+      <x:c r="D4" s="30" t="n">
         <x:v>2019</x:v>
       </x:c>
-      <x:c r="E4" s="46" t="str">
+      <x:c r="E4" s="24" t="str">
         <x:v>Xiphias gladius</x:v>
       </x:c>
-      <x:c r="F4" s="46" t="str">
+      <x:c r="F4" s="24" t="str">
         <x:v>Swordfish</x:v>
       </x:c>
-      <x:c r="G4" s="46" t="str">
+      <x:c r="G4" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="H4" s="46" t="str">
+      <x:c r="H4" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="I4" s="60" t="n">
+      <x:c r="I4" s="31" t="n">
         <x:v>2796.2833721928</x:v>
       </x:c>
-      <x:c r="J4" s="60" t="n">
+      <x:c r="J4" s="31" t="n">
         <x:v>1985.9674615852</x:v>
       </x:c>
-      <x:c r="K4" s="60" t="n">
+      <x:c r="K4" s="31" t="n">
         <x:v>810.3159106076</x:v>
       </x:c>
-      <x:c r="L4" s="60" t="n">
+      <x:c r="L4" s="31" t="n">
         <x:v>1985.9674615852</x:v>
       </x:c>
-      <x:c r="M4" s="60" t="n">
+      <x:c r="M4" s="31" t="n">
         <x:v>810.3159106076</x:v>
       </x:c>
-      <x:c r="N4" s="46" t="str">
+      <x:c r="N4" s="24" t="str">
         <x:v>xiphias gladius</x:v>
       </x:c>
-      <x:c r="O4" s="62" t="n">
+      <x:c r="O4" s="32" t="n">
         <x:v>4.53</x:v>
       </x:c>
-      <x:c r="P4" s="46" t="str">
+      <x:c r="P4" s="24" t="str">
         <x:v>exact_2020_supplement</x:v>
       </x:c>
-      <x:c r="Q4" s="62" t="str">
+      <x:c r="Q4" s="32" t="str">
         <x:v>2020 supplement MeanTL</x:v>
       </x:c>
-      <x:c r="R4" s="46" t="str">
+      <x:c r="R4" s="24" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="S4" s="46" t="str">
+      <x:c r="S4" s="24" t="str">
         <x:v>Xiphias gladius</x:v>
       </x:c>
-      <x:c r="T4" s="62" t="n">
+      <x:c r="T4" s="32" t="n">
         <x:f>IF(O4="","",(1/'Metadata'!$B$5)^(O4-1))</x:f>
         <x:v>3388.4415613920273</x:v>
       </x:c>
-      <x:c r="U4" s="60" t="n">
+      <x:c r="U4" s="31" t="n">
         <x:f>IF(T4="","",I4*T4)</x:f>
         <x:v>9475042.795767535</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
-      <x:c r="A5" s="46" t="str">
-        <x:v>HS_081</x:v>
-      </x:c>
-      <x:c r="B5" s="46" t="str">
+      <x:c r="A5" s="24" t="str">
+        <x:v>HS_081</x:v>
+      </x:c>
+      <x:c r="B5" s="24" t="str">
         <x:v>Pacific, Southwest</x:v>
       </x:c>
-      <x:c r="C5" s="46" t="str">
+      <x:c r="C5" s="24" t="str">
         <x:v>High Seas</x:v>
       </x:c>
-      <x:c r="D5" s="58" t="n">
+      <x:c r="D5" s="30" t="n">
         <x:v>2019</x:v>
       </x:c>
-      <x:c r="E5" s="46" t="str">
+      <x:c r="E5" s="24" t="str">
         <x:v>Thunnus maccoyii</x:v>
       </x:c>
-      <x:c r="F5" s="46" t="str">
+      <x:c r="F5" s="24" t="str">
         <x:v>Southern bluefin tuna</x:v>
       </x:c>
-      <x:c r="G5" s="46" t="str">
+      <x:c r="G5" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="H5" s="46" t="str">
+      <x:c r="H5" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="I5" s="60" t="n">
+      <x:c r="I5" s="31" t="n">
         <x:v>2508.3072798526</x:v>
       </x:c>
-      <x:c r="J5" s="60" t="n">
+      <x:c r="J5" s="31" t="n">
         <x:v>2506.5600056156</x:v>
       </x:c>
-      <x:c r="K5" s="60" t="n">
+      <x:c r="K5" s="31" t="n">
         <x:v>1.747274237</x:v>
       </x:c>
-      <x:c r="L5" s="60" t="n">
+      <x:c r="L5" s="31" t="n">
         <x:v>2506.5600056156</x:v>
       </x:c>
-      <x:c r="M5" s="60" t="n">
+      <x:c r="M5" s="31" t="n">
         <x:v>1.747274237</x:v>
       </x:c>
-      <x:c r="N5" s="46" t="str">
+      <x:c r="N5" s="24" t="str">
         <x:v>thunnus maccoyii</x:v>
       </x:c>
-      <x:c r="O5" s="62" t="n">
+      <x:c r="O5" s="32" t="n">
         <x:v>3.93</x:v>
       </x:c>
-      <x:c r="P5" s="46" t="str">
+      <x:c r="P5" s="24" t="str">
         <x:v>exact_2020_supplement</x:v>
       </x:c>
-      <x:c r="Q5" s="62" t="str">
+      <x:c r="Q5" s="32" t="str">
         <x:v>2020 supplement MeanTL</x:v>
       </x:c>
-      <x:c r="R5" s="46" t="str">
+      <x:c r="R5" s="24" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="S5" s="46" t="str">
+      <x:c r="S5" s="24" t="str">
         <x:v>Thunnus maccoyii</x:v>
       </x:c>
-      <x:c r="T5" s="62" t="n">
+      <x:c r="T5" s="32" t="n">
         <x:f>IF(O5="","",(1/'Metadata'!$B$5)^(O5-1))</x:f>
         <x:v>851.1380382023768</x:v>
       </x:c>
-      <x:c r="U5" s="60" t="n">
+      <x:c r="U5" s="31" t="n">
         <x:f>IF(T5="","",I5*T5)</x:f>
         <x:v>2134915.7373824823</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
-      <x:c r="A6" s="46" t="str">
-        <x:v>HS_081</x:v>
-      </x:c>
-      <x:c r="B6" s="46" t="str">
+      <x:c r="A6" s="24" t="str">
+        <x:v>HS_081</x:v>
+      </x:c>
+      <x:c r="B6" s="24" t="str">
         <x:v>Pacific, Southwest</x:v>
       </x:c>
-      <x:c r="C6" s="46" t="str">
+      <x:c r="C6" s="24" t="str">
         <x:v>High Seas</x:v>
       </x:c>
-      <x:c r="D6" s="58" t="n">
+      <x:c r="D6" s="30" t="n">
         <x:v>2019</x:v>
       </x:c>
-      <x:c r="E6" s="46" t="str">
+      <x:c r="E6" s="24" t="str">
         <x:v>Marine fishes not identified</x:v>
       </x:c>
-      <x:c r="F6" s="46" t="str">
+      <x:c r="F6" s="24" t="str">
         <x:v>Marine fishes nei</x:v>
       </x:c>
-      <x:c r="G6" s="46" t="str">
+      <x:c r="G6" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="H6" s="46" t="str">
+      <x:c r="H6" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="I6" s="60" t="n">
+      <x:c r="I6" s="31" t="n">
         <x:v>2429.5427242088</x:v>
       </x:c>
-      <x:c r="J6" s="60" t="n">
+      <x:c r="J6" s="31" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K6" s="60" t="n">
+      <x:c r="K6" s="31" t="n">
         <x:v>2429.5427242088</x:v>
       </x:c>
-      <x:c r="L6" s="60" t="n">
+      <x:c r="L6" s="31" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M6" s="60" t="n">
+      <x:c r="M6" s="31" t="n">
         <x:v>2429.5427242088</x:v>
       </x:c>
-      <x:c r="N6" s="46" t="str">
+      <x:c r="N6" s="24" t="str">
         <x:v>marine fishes not identified</x:v>
       </x:c>
-      <x:c r="O6" s="62" t="n">
+      <x:c r="O6" s="32" t="n">
         <x:v>3.28</x:v>
       </x:c>
-      <x:c r="P6" s="46" t="str">
+      <x:c r="P6" s="24" t="str">
         <x:v>exact_sea_around_us</x:v>
       </x:c>
-      <x:c r="Q6" s="62" t="str">
+      <x:c r="Q6" s="32" t="str">
         <x:v>Sea Around Us exploited organisms</x:v>
       </x:c>
-      <x:c r="R6" s="46" t="str">
+      <x:c r="R6" s="24" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="S6" s="46" t="str">
+      <x:c r="S6" s="24" t="str">
         <x:v>Marine fishes not identified</x:v>
       </x:c>
-      <x:c r="T6" s="62" t="n">
+      <x:c r="T6" s="32" t="n">
         <x:f>IF(O6="","",(1/'Metadata'!$B$5)^(O6-1))</x:f>
         <x:v>190.54607179632464</x:v>
       </x:c>
-      <x:c r="U6" s="60" t="n">
+      <x:c r="U6" s="31" t="n">
         <x:f>IF(T6="","",I6*T6)</x:f>
         <x:v>462939.82235932816</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
-      <x:c r="A7" s="46" t="str">
-        <x:v>HS_081</x:v>
-      </x:c>
-      <x:c r="B7" s="46" t="str">
+      <x:c r="A7" s="24" t="str">
+        <x:v>HS_081</x:v>
+      </x:c>
+      <x:c r="B7" s="24" t="str">
         <x:v>Pacific, Southwest</x:v>
       </x:c>
-      <x:c r="C7" s="46" t="str">
+      <x:c r="C7" s="24" t="str">
         <x:v>High Seas</x:v>
       </x:c>
-      <x:c r="D7" s="58" t="n">
+      <x:c r="D7" s="30" t="n">
         <x:v>2019</x:v>
       </x:c>
-      <x:c r="E7" s="46" t="str">
+      <x:c r="E7" s="24" t="str">
         <x:v>Thunnus albacares</x:v>
       </x:c>
-      <x:c r="F7" s="46" t="str">
+      <x:c r="F7" s="24" t="str">
         <x:v>Yellowfin tuna</x:v>
       </x:c>
-      <x:c r="G7" s="46" t="str">
+      <x:c r="G7" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="H7" s="46" t="str">
+      <x:c r="H7" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="I7" s="60" t="n">
+      <x:c r="I7" s="31" t="n">
         <x:v>1728.6708196007</x:v>
       </x:c>
-      <x:c r="J7" s="60" t="n">
+      <x:c r="J7" s="31" t="n">
         <x:v>1669.6590504997</x:v>
       </x:c>
-      <x:c r="K7" s="60" t="n">
+      <x:c r="K7" s="31" t="n">
         <x:v>59.011769101</x:v>
       </x:c>
-      <x:c r="L7" s="60" t="n">
+      <x:c r="L7" s="31" t="n">
         <x:v>1669.6590504997</x:v>
       </x:c>
-      <x:c r="M7" s="60" t="n">
+      <x:c r="M7" s="31" t="n">
         <x:v>59.011769101</x:v>
       </x:c>
-      <x:c r="N7" s="46" t="str">
+      <x:c r="N7" s="24" t="str">
         <x:v>thunnus albacares</x:v>
       </x:c>
-      <x:c r="O7" s="62" t="n">
+      <x:c r="O7" s="32" t="n">
         <x:v>4.41</x:v>
       </x:c>
-      <x:c r="P7" s="46" t="str">
+      <x:c r="P7" s="24" t="str">
         <x:v>exact_2020_supplement</x:v>
       </x:c>
-      <x:c r="Q7" s="62" t="str">
+      <x:c r="Q7" s="32" t="str">
         <x:v>2020 supplement MeanTL</x:v>
       </x:c>
-      <x:c r="R7" s="46" t="str">
+      <x:c r="R7" s="24" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="S7" s="46" t="str">
+      <x:c r="S7" s="24" t="str">
         <x:v>Thunnus albacares</x:v>
       </x:c>
-      <x:c r="T7" s="62" t="n">
+      <x:c r="T7" s="32" t="n">
         <x:f>IF(O7="","",(1/'Metadata'!$B$5)^(O7-1))</x:f>
         <x:v>2570.3957827688646</x:v>
       </x:c>
-      <x:c r="U7" s="60" t="n">
+      <x:c r="U7" s="31" t="n">
         <x:f>IF(T7="","",I7*T7)</x:f>
         <x:v>4443368.184497236</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
-      <x:c r="A8" s="46" t="str">
-        <x:v>HS_081</x:v>
-      </x:c>
-      <x:c r="B8" s="46" t="str">
+      <x:c r="A8" s="24" t="str">
+        <x:v>HS_081</x:v>
+      </x:c>
+      <x:c r="B8" s="24" t="str">
         <x:v>Pacific, Southwest</x:v>
       </x:c>
-      <x:c r="C8" s="46" t="str">
+      <x:c r="C8" s="24" t="str">
         <x:v>High Seas</x:v>
       </x:c>
-      <x:c r="D8" s="58" t="n">
+      <x:c r="D8" s="30" t="n">
         <x:v>2019</x:v>
       </x:c>
-      <x:c r="E8" s="46" t="str">
+      <x:c r="E8" s="24" t="str">
         <x:v>Elasmobranchii</x:v>
       </x:c>
-      <x:c r="F8" s="46" t="str">
+      <x:c r="F8" s="24" t="str">
         <x:v>Sharks, rays, skates</x:v>
       </x:c>
-      <x:c r="G8" s="46" t="str">
+      <x:c r="G8" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="H8" s="46" t="str">
+      <x:c r="H8" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="I8" s="60" t="n">
+      <x:c r="I8" s="31" t="n">
         <x:v>1323.4777613404</x:v>
       </x:c>
-      <x:c r="J8" s="60" t="n">
+      <x:c r="J8" s="31" t="n">
         <x:v>1287.4913929822</x:v>
       </x:c>
-      <x:c r="K8" s="60" t="n">
+      <x:c r="K8" s="31" t="n">
         <x:v>35.9863683582</x:v>
       </x:c>
-      <x:c r="L8" s="60" t="n">
+      <x:c r="L8" s="31" t="n">
         <x:v>1287.4913929822</x:v>
       </x:c>
-      <x:c r="M8" s="60" t="n">
+      <x:c r="M8" s="31" t="n">
         <x:v>35.9863683582</x:v>
       </x:c>
-      <x:c r="N8" s="46" t="str">
+      <x:c r="N8" s="24" t="str">
         <x:v>elasmobranchii</x:v>
       </x:c>
-      <x:c r="O8" s="62" t="n">
+      <x:c r="O8" s="32" t="n">
         <x:v>4.05</x:v>
       </x:c>
-      <x:c r="P8" s="46" t="str">
+      <x:c r="P8" s="24" t="str">
         <x:v>exact_sea_around_us</x:v>
       </x:c>
-      <x:c r="Q8" s="62" t="str">
+      <x:c r="Q8" s="32" t="str">
         <x:v>Sea Around Us exploited organisms</x:v>
       </x:c>
-      <x:c r="R8" s="46" t="str">
+      <x:c r="R8" s="24" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="S8" s="46" t="str">
+      <x:c r="S8" s="24" t="str">
         <x:v>Elasmobranchii</x:v>
       </x:c>
-      <x:c r="T8" s="62" t="n">
+      <x:c r="T8" s="32" t="n">
         <x:f>IF(O8="","",(1/'Metadata'!$B$5)^(O8-1))</x:f>
         <x:v>1122.018454301963</x:v>
       </x:c>
-      <x:c r="U8" s="60" t="n">
+      <x:c r="U8" s="31" t="n">
         <x:f>IF(T8="","",I8*T8)</x:f>
         <x:v>1484966.4720821779</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
-      <x:c r="A9" s="46" t="str">
-        <x:v>HS_081</x:v>
-      </x:c>
-      <x:c r="B9" s="46" t="str">
+      <x:c r="A9" s="24" t="str">
+        <x:v>HS_081</x:v>
+      </x:c>
+      <x:c r="B9" s="24" t="str">
         <x:v>Pacific, Southwest</x:v>
       </x:c>
-      <x:c r="C9" s="46" t="str">
+      <x:c r="C9" s="24" t="str">
         <x:v>High Seas</x:v>
       </x:c>
-      <x:c r="D9" s="58" t="n">
+      <x:c r="D9" s="30" t="n">
         <x:v>2019</x:v>
       </x:c>
-      <x:c r="E9" s="46" t="str">
+      <x:c r="E9" s="24" t="str">
         <x:v>Marine pelagic fishes not identified</x:v>
       </x:c>
-      <x:c r="F9" s="46" t="str">
+      <x:c r="F9" s="24" t="str">
         <x:v>Pelagic fishes</x:v>
       </x:c>
-      <x:c r="G9" s="46" t="str">
+      <x:c r="G9" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="H9" s="46" t="str">
+      <x:c r="H9" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="I9" s="60" t="n">
+      <x:c r="I9" s="31" t="n">
         <x:v>1062.9224634476</x:v>
       </x:c>
-      <x:c r="J9" s="60" t="n">
+      <x:c r="J9" s="31" t="n">
         <x:v>231.3785395967</x:v>
       </x:c>
-      <x:c r="K9" s="60" t="n">
+      <x:c r="K9" s="31" t="n">
         <x:v>831.5439238509</x:v>
       </x:c>
-      <x:c r="L9" s="60" t="n">
+      <x:c r="L9" s="31" t="n">
         <x:v>231.3785395967</x:v>
       </x:c>
-      <x:c r="M9" s="60" t="n">
+      <x:c r="M9" s="31" t="n">
         <x:v>831.5439238509</x:v>
       </x:c>
-      <x:c r="N9" s="46" t="str">
+      <x:c r="N9" s="24" t="str">
         <x:v>marine pelagic fishes not identified</x:v>
       </x:c>
-      <x:c r="O9" s="62" t="n">
+      <x:c r="O9" s="32" t="n">
         <x:v>3.35</x:v>
       </x:c>
-      <x:c r="P9" s="46" t="str">
+      <x:c r="P9" s="24" t="str">
         <x:v>exact_sea_around_us</x:v>
       </x:c>
-      <x:c r="Q9" s="62" t="str">
+      <x:c r="Q9" s="32" t="str">
         <x:v>Sea Around Us exploited organisms</x:v>
       </x:c>
-      <x:c r="R9" s="46" t="str">
+      <x:c r="R9" s="24" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="S9" s="46" t="str">
+      <x:c r="S9" s="24" t="str">
         <x:v>Marine pelagic fishes not identified</x:v>
       </x:c>
-      <x:c r="T9" s="62" t="n">
+      <x:c r="T9" s="32" t="n">
         <x:f>IF(O9="","",(1/'Metadata'!$B$5)^(O9-1))</x:f>
         <x:v>223.872113856834</x:v>
       </x:c>
-      <x:c r="U9" s="60" t="n">
+      <x:c r="U9" s="31" t="n">
         <x:f>IF(T9="","",I9*T9)</x:f>
         <x:v>237958.69875792757</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
-      <x:c r="A10" s="46" t="str">
-        <x:v>HS_081</x:v>
-      </x:c>
-      <x:c r="B10" s="46" t="str">
+      <x:c r="A10" s="24" t="str">
+        <x:v>HS_081</x:v>
+      </x:c>
+      <x:c r="B10" s="24" t="str">
         <x:v>Pacific, Southwest</x:v>
       </x:c>
-      <x:c r="C10" s="46" t="str">
+      <x:c r="C10" s="24" t="str">
         <x:v>High Seas</x:v>
       </x:c>
-      <x:c r="D10" s="58" t="n">
+      <x:c r="D10" s="30" t="n">
         <x:v>2019</x:v>
       </x:c>
-      <x:c r="E10" s="46" t="str">
+      <x:c r="E10" s="24" t="str">
         <x:v>Thunnus obesus</x:v>
       </x:c>
-      <x:c r="F10" s="46" t="str">
+      <x:c r="F10" s="24" t="str">
         <x:v>Bigeye tuna</x:v>
       </x:c>
-      <x:c r="G10" s="46" t="str">
+      <x:c r="G10" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="H10" s="46" t="str">
+      <x:c r="H10" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="I10" s="60" t="n">
+      <x:c r="I10" s="31" t="n">
         <x:v>967.1130531046</x:v>
       </x:c>
-      <x:c r="J10" s="60" t="n">
+      <x:c r="J10" s="31" t="n">
         <x:v>900.9191162033001</x:v>
       </x:c>
-      <x:c r="K10" s="60" t="n">
+      <x:c r="K10" s="31" t="n">
         <x:v>66.19393690129999</x:v>
       </x:c>
-      <x:c r="L10" s="60" t="n">
+      <x:c r="L10" s="31" t="n">
         <x:v>900.9191162033001</x:v>
       </x:c>
-      <x:c r="M10" s="60" t="n">
+      <x:c r="M10" s="31" t="n">
         <x:v>66.19393690129999</x:v>
       </x:c>
-      <x:c r="N10" s="46" t="str">
+      <x:c r="N10" s="24" t="str">
         <x:v>thunnus obesus</x:v>
       </x:c>
-      <x:c r="O10" s="62" t="n">
+      <x:c r="O10" s="32" t="n">
         <x:v>4.49</x:v>
       </x:c>
-      <x:c r="P10" s="46" t="str">
+      <x:c r="P10" s="24" t="str">
         <x:v>exact_2020_supplement</x:v>
       </x:c>
-      <x:c r="Q10" s="62" t="str">
+      <x:c r="Q10" s="32" t="str">
         <x:v>2020 supplement MeanTL</x:v>
       </x:c>
-      <x:c r="R10" s="46" t="str">
+      <x:c r="R10" s="24" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="S10" s="46" t="str">
+      <x:c r="S10" s="24" t="str">
         <x:v>Thunnus obesus</x:v>
       </x:c>
-      <x:c r="T10" s="62" t="n">
+      <x:c r="T10" s="32" t="n">
         <x:f>IF(O10="","",(1/'Metadata'!$B$5)^(O10-1))</x:f>
         <x:v>3090.295432513592</x:v>
       </x:c>
-      <x:c r="U10" s="60" t="n">
+      <x:c r="U10" s="31" t="n">
         <x:f>IF(T10="","",I10*T10)</x:f>
         <x:v>2988665.0507334205</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
-      <x:c r="A11" s="46" t="str">
-        <x:v>HS_081</x:v>
-      </x:c>
-      <x:c r="B11" s="46" t="str">
+      <x:c r="A11" s="24" t="str">
+        <x:v>HS_081</x:v>
+      </x:c>
+      <x:c r="B11" s="24" t="str">
         <x:v>Pacific, Southwest</x:v>
       </x:c>
-      <x:c r="C11" s="46" t="str">
+      <x:c r="C11" s="24" t="str">
         <x:v>High Seas</x:v>
       </x:c>
-      <x:c r="D11" s="58" t="n">
+      <x:c r="D11" s="30" t="n">
         <x:v>2019</x:v>
       </x:c>
-      <x:c r="E11" s="46" t="str">
+      <x:c r="E11" s="24" t="str">
         <x:v>Isurus</x:v>
       </x:c>
-      <x:c r="F11" s="46" t="str">
+      <x:c r="F11" s="24" t="str">
         <x:v>Mako sharks</x:v>
       </x:c>
-      <x:c r="G11" s="46" t="str">
+      <x:c r="G11" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="H11" s="46" t="str">
+      <x:c r="H11" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="I11" s="60" t="n">
+      <x:c r="I11" s="31" t="n">
         <x:v>856.7142914668999</x:v>
       </x:c>
-      <x:c r="J11" s="60" t="n">
+      <x:c r="J11" s="31" t="n">
         <x:v>205.6400183152</x:v>
       </x:c>
-      <x:c r="K11" s="60" t="n">
+      <x:c r="K11" s="31" t="n">
         <x:v>651.0742731517</x:v>
       </x:c>
-      <x:c r="L11" s="60" t="n">
+      <x:c r="L11" s="31" t="n">
         <x:v>205.6400183152</x:v>
       </x:c>
-      <x:c r="M11" s="60" t="n">
+      <x:c r="M11" s="31" t="n">
         <x:v>651.0742731517</x:v>
       </x:c>
-      <x:c r="N11" s="46" t="str">
+      <x:c r="N11" s="24" t="str">
         <x:v>isurus</x:v>
       </x:c>
-      <x:c r="O11" s="62" t="n">
+      <x:c r="O11" s="32" t="n">
         <x:v>4.5</x:v>
       </x:c>
-      <x:c r="P11" s="46" t="str">
+      <x:c r="P11" s="24" t="str">
         <x:v>exact_sea_around_us</x:v>
       </x:c>
-      <x:c r="Q11" s="62" t="str">
+      <x:c r="Q11" s="32" t="str">
         <x:v>Sea Around Us exploited organisms</x:v>
       </x:c>
-      <x:c r="R11" s="46" t="str">
+      <x:c r="R11" s="24" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="S11" s="46" t="str">
+      <x:c r="S11" s="24" t="str">
         <x:v>Isurus</x:v>
       </x:c>
-      <x:c r="T11" s="62" t="n">
+      <x:c r="T11" s="32" t="n">
         <x:f>IF(O11="","",(1/'Metadata'!$B$5)^(O11-1))</x:f>
         <x:v>3162.2776601683795</x:v>
       </x:c>
-      <x:c r="U11" s="60" t="n">
+      <x:c r="U11" s="31" t="n">
         <x:f>IF(T11="","",I11*T11)</x:f>
         <x:v>2709168.4650527593</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
-      <x:c r="A12" s="46" t="str">
-        <x:v>HS_081</x:v>
-      </x:c>
-      <x:c r="B12" s="46" t="str">
+      <x:c r="A12" s="24" t="str">
+        <x:v>HS_081</x:v>
+      </x:c>
+      <x:c r="B12" s="24" t="str">
         <x:v>Pacific, Southwest</x:v>
       </x:c>
-      <x:c r="C12" s="46" t="str">
+      <x:c r="C12" s="24" t="str">
         <x:v>High Seas</x:v>
       </x:c>
-      <x:c r="D12" s="58" t="n">
+      <x:c r="D12" s="30" t="n">
         <x:v>2019</x:v>
       </x:c>
-      <x:c r="E12" s="46" t="str">
+      <x:c r="E12" s="24" t="str">
         <x:v>Katsuwonus pelamis</x:v>
       </x:c>
-      <x:c r="F12" s="46" t="str">
+      <x:c r="F12" s="24" t="str">
         <x:v>Skipjack tuna</x:v>
       </x:c>
-      <x:c r="G12" s="46" t="str">
+      <x:c r="G12" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="H12" s="46" t="str">
+      <x:c r="H12" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="I12" s="60" t="n">
+      <x:c r="I12" s="31" t="n">
         <x:v>811.0170452826001</x:v>
       </x:c>
-      <x:c r="J12" s="60" t="n">
+      <x:c r="J12" s="31" t="n">
         <x:v>800.0222932435</x:v>
       </x:c>
-      <x:c r="K12" s="60" t="n">
+      <x:c r="K12" s="31" t="n">
         <x:v>10.9947520391</x:v>
       </x:c>
-      <x:c r="L12" s="60" t="n">
+      <x:c r="L12" s="31" t="n">
         <x:v>800.0222932435</x:v>
       </x:c>
-      <x:c r="M12" s="60" t="n">
+      <x:c r="M12" s="31" t="n">
         <x:v>10.9947520391</x:v>
       </x:c>
-      <x:c r="N12" s="46" t="str">
+      <x:c r="N12" s="24" t="str">
         <x:v>katsuwonus pelamis</x:v>
       </x:c>
-      <x:c r="O12" s="62" t="n">
+      <x:c r="O12" s="32" t="n">
         <x:v>4.43</x:v>
       </x:c>
-      <x:c r="P12" s="46" t="str">
+      <x:c r="P12" s="24" t="str">
         <x:v>exact_2020_supplement</x:v>
       </x:c>
-      <x:c r="Q12" s="62" t="str">
+      <x:c r="Q12" s="32" t="str">
         <x:v>2020 supplement MeanTL</x:v>
       </x:c>
-      <x:c r="R12" s="46" t="str">
+      <x:c r="R12" s="24" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="S12" s="46" t="str">
+      <x:c r="S12" s="24" t="str">
         <x:v>Katsuwonus pelamis</x:v>
       </x:c>
-      <x:c r="T12" s="62" t="n">
+      <x:c r="T12" s="32" t="n">
         <x:f>IF(O12="","",(1/'Metadata'!$B$5)^(O12-1))</x:f>
         <x:v>2691.534803926914</x:v>
       </x:c>
-      <x:c r="U12" s="60" t="n">
+      <x:c r="U12" s="31" t="n">
         <x:f>IF(T12="","",I12*T12)</x:f>
         <x:v>2182880.603956088</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
-      <x:c r="A13" s="46" t="str">
-        <x:v>HS_081</x:v>
-      </x:c>
-      <x:c r="B13" s="46" t="str">
+      <x:c r="A13" s="24" t="str">
+        <x:v>HS_081</x:v>
+      </x:c>
+      <x:c r="B13" s="24" t="str">
         <x:v>Pacific, Southwest</x:v>
       </x:c>
-      <x:c r="C13" s="46" t="str">
+      <x:c r="C13" s="24" t="str">
         <x:v>High Seas</x:v>
       </x:c>
-      <x:c r="D13" s="58" t="n">
+      <x:c r="D13" s="30" t="n">
         <x:v>2019</x:v>
       </x:c>
-      <x:c r="E13" s="46" t="str">
+      <x:c r="E13" s="24" t="str">
         <x:v>Scombridae</x:v>
       </x:c>
-      <x:c r="F13" s="46" t="str">
+      <x:c r="F13" s="24" t="str">
         <x:v>Mackerels, tunas, bonitos</x:v>
       </x:c>
-      <x:c r="G13" s="46" t="str">
+      <x:c r="G13" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="H13" s="46" t="str">
+      <x:c r="H13" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="I13" s="60" t="n">
+      <x:c r="I13" s="31" t="n">
         <x:v>650.0094576147001</x:v>
       </x:c>
-      <x:c r="J13" s="60" t="n">
+      <x:c r="J13" s="31" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K13" s="60" t="n">
+      <x:c r="K13" s="31" t="n">
         <x:v>650.0094576147001</x:v>
       </x:c>
-      <x:c r="L13" s="60" t="n">
+      <x:c r="L13" s="31" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M13" s="60" t="n">
+      <x:c r="M13" s="31" t="n">
         <x:v>650.0094576147001</x:v>
       </x:c>
-      <x:c r="N13" s="46" t="str">
+      <x:c r="N13" s="24" t="str">
         <x:v>scombridae</x:v>
       </x:c>
-      <x:c r="O13" s="62" t="n">
+      <x:c r="O13" s="32" t="n">
         <x:v>4.26</x:v>
       </x:c>
-      <x:c r="P13" s="46" t="str">
+      <x:c r="P13" s="24" t="str">
         <x:v>exact_sea_around_us</x:v>
       </x:c>
-      <x:c r="Q13" s="62" t="str">
+      <x:c r="Q13" s="32" t="str">
         <x:v>Sea Around Us exploited organisms</x:v>
       </x:c>
-      <x:c r="R13" s="46" t="str">
+      <x:c r="R13" s="24" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="S13" s="46" t="str">
+      <x:c r="S13" s="24" t="str">
         <x:v>Scombridae</x:v>
       </x:c>
-      <x:c r="T13" s="62" t="n">
+      <x:c r="T13" s="32" t="n">
         <x:f>IF(O13="","",(1/'Metadata'!$B$5)^(O13-1))</x:f>
         <x:v>1819.7008586099826</x:v>
       </x:c>
-      <x:c r="U13" s="60" t="n">
+      <x:c r="U13" s="31" t="n">
         <x:f>IF(T13="","",I13*T13)</x:f>
         <x:v>1182822.7681260789</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
-      <x:c r="A14" s="46" t="str">
-        <x:v>HS_081</x:v>
-      </x:c>
-      <x:c r="B14" s="46" t="str">
+      <x:c r="A14" s="24" t="str">
+        <x:v>HS_081</x:v>
+      </x:c>
+      <x:c r="B14" s="24" t="str">
         <x:v>Pacific, Southwest</x:v>
       </x:c>
-      <x:c r="C14" s="46" t="str">
+      <x:c r="C14" s="24" t="str">
         <x:v>High Seas</x:v>
       </x:c>
-      <x:c r="D14" s="58" t="n">
+      <x:c r="D14" s="30" t="n">
         <x:v>2019</x:v>
       </x:c>
-      <x:c r="E14" s="46" t="str">
+      <x:c r="E14" s="24" t="str">
         <x:v>Kajikia audax</x:v>
       </x:c>
-      <x:c r="F14" s="46" t="str">
+      <x:c r="F14" s="24" t="str">
         <x:v>Striped marlin</x:v>
       </x:c>
-      <x:c r="G14" s="46" t="str">
+      <x:c r="G14" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="H14" s="46" t="str">
+      <x:c r="H14" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="I14" s="60" t="n">
+      <x:c r="I14" s="31" t="n">
         <x:v>611.2168521866</x:v>
       </x:c>
-      <x:c r="J14" s="60" t="n">
+      <x:c r="J14" s="31" t="n">
         <x:v>611.2168521866</x:v>
       </x:c>
-      <x:c r="K14" s="60" t="n">
+      <x:c r="K14" s="31" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L14" s="60" t="n">
+      <x:c r="L14" s="31" t="n">
         <x:v>611.2168521866</x:v>
       </x:c>
-      <x:c r="M14" s="60" t="n">
+      <x:c r="M14" s="31" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N14" s="46" t="str">
+      <x:c r="N14" s="24" t="str">
         <x:v>kajikia audax</x:v>
       </x:c>
-      <x:c r="O14" s="62" t="n">
+      <x:c r="O14" s="32" t="n">
         <x:v>4.58</x:v>
       </x:c>
-      <x:c r="P14" s="46" t="str">
+      <x:c r="P14" s="24" t="str">
         <x:v>exact_2020_supplement</x:v>
       </x:c>
-      <x:c r="Q14" s="62" t="str">
+      <x:c r="Q14" s="32" t="str">
         <x:v>2020 supplement MeanTL</x:v>
       </x:c>
-      <x:c r="R14" s="46" t="str">
+      <x:c r="R14" s="24" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="S14" s="46" t="str">
+      <x:c r="S14" s="24" t="str">
         <x:v>Kajikia audax</x:v>
       </x:c>
-      <x:c r="T14" s="62" t="n">
+      <x:c r="T14" s="32" t="n">
         <x:f>IF(O14="","",(1/'Metadata'!$B$5)^(O14-1))</x:f>
         <x:v>3801.8939632056126</x:v>
       </x:c>
-      <x:c r="U14" s="60" t="n">
+      <x:c r="U14" s="31" t="n">
         <x:f>IF(T14="","",I14*T14)</x:f>
         <x:v>2323781.660537772</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
-      <x:c r="A15" s="46" t="str">
-        <x:v>HS_081</x:v>
-      </x:c>
-      <x:c r="B15" s="46" t="str">
+      <x:c r="A15" s="24" t="str">
+        <x:v>HS_081</x:v>
+      </x:c>
+      <x:c r="B15" s="24" t="str">
         <x:v>Pacific, Southwest</x:v>
       </x:c>
-      <x:c r="C15" s="46" t="str">
+      <x:c r="C15" s="24" t="str">
         <x:v>High Seas</x:v>
       </x:c>
-      <x:c r="D15" s="58" t="n">
+      <x:c r="D15" s="30" t="n">
         <x:v>2019</x:v>
       </x:c>
-      <x:c r="E15" s="46" t="str">
+      <x:c r="E15" s="24" t="str">
         <x:v>Carcharhinus longimanus</x:v>
       </x:c>
-      <x:c r="F15" s="46" t="str">
+      <x:c r="F15" s="24" t="str">
         <x:v>Oceanic whitetip shark</x:v>
       </x:c>
-      <x:c r="G15" s="46" t="str">
+      <x:c r="G15" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="H15" s="46" t="str">
+      <x:c r="H15" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="I15" s="60" t="n">
+      <x:c r="I15" s="31" t="n">
         <x:v>254.01856427869998</x:v>
       </x:c>
-      <x:c r="J15" s="60" t="n">
+      <x:c r="J15" s="31" t="n">
         <x:v>23.9844482655</x:v>
       </x:c>
-      <x:c r="K15" s="60" t="n">
+      <x:c r="K15" s="31" t="n">
         <x:v>230.0341160132</x:v>
       </x:c>
-      <x:c r="L15" s="60" t="n">
+      <x:c r="L15" s="31" t="n">
         <x:v>23.9844482655</x:v>
       </x:c>
-      <x:c r="M15" s="60" t="n">
+      <x:c r="M15" s="31" t="n">
         <x:v>230.0341160132</x:v>
       </x:c>
-      <x:c r="N15" s="46" t="str">
+      <x:c r="N15" s="24" t="str">
         <x:v>carcharhinus longimanus</x:v>
       </x:c>
-      <x:c r="O15" s="62" t="n">
+      <x:c r="O15" s="32" t="n">
         <x:v>4.16</x:v>
       </x:c>
-      <x:c r="P15" s="46" t="str">
+      <x:c r="P15" s="24" t="str">
         <x:v>exact_2020_supplement</x:v>
       </x:c>
-      <x:c r="Q15" s="62" t="str">
+      <x:c r="Q15" s="32" t="str">
         <x:v>2020 supplement MeanTL</x:v>
       </x:c>
-      <x:c r="R15" s="46" t="str">
+      <x:c r="R15" s="24" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="S15" s="46" t="str">
+      <x:c r="S15" s="24" t="str">
         <x:v>Carcharhinus longimanus</x:v>
       </x:c>
-      <x:c r="T15" s="62" t="n">
+      <x:c r="T15" s="32" t="n">
         <x:f>IF(O15="","",(1/'Metadata'!$B$5)^(O15-1))</x:f>
         <x:v>1445.439770745928</x:v>
       </x:c>
-      <x:c r="U15" s="60" t="n">
+      <x:c r="U15" s="31" t="n">
         <x:f>IF(T15="","",I15*T15)</x:f>
         <x:v>367168.53531621385</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
-      <x:c r="A16" s="46" t="str">
-        <x:v>HS_081</x:v>
-      </x:c>
-      <x:c r="B16" s="46" t="str">
+      <x:c r="A16" s="24" t="str">
+        <x:v>HS_081</x:v>
+      </x:c>
+      <x:c r="B16" s="24" t="str">
         <x:v>Pacific, Southwest</x:v>
       </x:c>
-      <x:c r="C16" s="46" t="str">
+      <x:c r="C16" s="24" t="str">
         <x:v>High Seas</x:v>
       </x:c>
-      <x:c r="D16" s="58" t="n">
+      <x:c r="D16" s="30" t="n">
         <x:v>2019</x:v>
       </x:c>
-      <x:c r="E16" s="46" t="str">
+      <x:c r="E16" s="24" t="str">
         <x:v>Thunnus orientalis</x:v>
       </x:c>
-      <x:c r="F16" s="46" t="str">
+      <x:c r="F16" s="24" t="str">
         <x:v>Pacific bluefin tuna</x:v>
       </x:c>
-      <x:c r="G16" s="46" t="str">
+      <x:c r="G16" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="H16" s="46" t="str">
+      <x:c r="H16" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="I16" s="60" t="n">
+      <x:c r="I16" s="31" t="n">
         <x:v>241.2116536481</x:v>
       </x:c>
-      <x:c r="J16" s="60" t="n">
+      <x:c r="J16" s="31" t="n">
         <x:v>238.6389799592</x:v>
       </x:c>
-      <x:c r="K16" s="60" t="n">
+      <x:c r="K16" s="31" t="n">
         <x:v>2.5726736889</x:v>
       </x:c>
-      <x:c r="L16" s="60" t="n">
+      <x:c r="L16" s="31" t="n">
         <x:v>238.6389799592</x:v>
       </x:c>
-      <x:c r="M16" s="60" t="n">
+      <x:c r="M16" s="31" t="n">
         <x:v>2.5726736889</x:v>
       </x:c>
-      <x:c r="N16" s="46" t="str">
+      <x:c r="N16" s="24" t="str">
         <x:v>thunnus orientalis</x:v>
       </x:c>
-      <x:c r="O16" s="62" t="n">
+      <x:c r="O16" s="32" t="n">
         <x:v>4.05</x:v>
       </x:c>
-      <x:c r="P16" s="46" t="str">
+      <x:c r="P16" s="24" t="str">
         <x:v>exact_2020_supplement</x:v>
       </x:c>
-      <x:c r="Q16" s="62" t="str">
+      <x:c r="Q16" s="32" t="str">
         <x:v>2020 supplement MeanTL</x:v>
       </x:c>
-      <x:c r="R16" s="46" t="str">
+      <x:c r="R16" s="24" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="S16" s="46" t="str">
+      <x:c r="S16" s="24" t="str">
         <x:v>Thunnus orientalis</x:v>
       </x:c>
-      <x:c r="T16" s="62" t="n">
+      <x:c r="T16" s="32" t="n">
         <x:f>IF(O16="","",(1/'Metadata'!$B$5)^(O16-1))</x:f>
         <x:v>1122.018454301963</x:v>
       </x:c>
-      <x:c r="U16" s="60" t="n">
+      <x:c r="U16" s="31" t="n">
         <x:f>IF(T16="","",I16*T16)</x:f>
         <x:v>270643.9267858616</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
-      <x:c r="A17" s="46" t="str">
-        <x:v>HS_081</x:v>
-      </x:c>
-      <x:c r="B17" s="46" t="str">
+      <x:c r="A17" s="24" t="str">
+        <x:v>HS_081</x:v>
+      </x:c>
+      <x:c r="B17" s="24" t="str">
         <x:v>Pacific, Southwest</x:v>
       </x:c>
-      <x:c r="C17" s="46" t="str">
+      <x:c r="C17" s="24" t="str">
         <x:v>High Seas</x:v>
       </x:c>
-      <x:c r="D17" s="58" t="n">
+      <x:c r="D17" s="30" t="n">
         <x:v>2019</x:v>
       </x:c>
-      <x:c r="E17" s="46" t="str">
+      <x:c r="E17" s="24" t="str">
         <x:v>Coryphaena hippurus</x:v>
       </x:c>
-      <x:c r="F17" s="46" t="str">
+      <x:c r="F17" s="24" t="str">
         <x:v>Common dolphinfish</x:v>
       </x:c>
-      <x:c r="G17" s="46" t="str">
+      <x:c r="G17" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="H17" s="46" t="str">
+      <x:c r="H17" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="I17" s="60" t="n">
+      <x:c r="I17" s="31" t="n">
         <x:v>231.8377033913</x:v>
       </x:c>
-      <x:c r="J17" s="60" t="n">
+      <x:c r="J17" s="31" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K17" s="60" t="n">
+      <x:c r="K17" s="31" t="n">
         <x:v>231.8377033913</x:v>
       </x:c>
-      <x:c r="L17" s="60" t="n">
+      <x:c r="L17" s="31" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M17" s="60" t="n">
+      <x:c r="M17" s="31" t="n">
         <x:v>231.8377033913</x:v>
       </x:c>
-      <x:c r="N17" s="46" t="str">
+      <x:c r="N17" s="24" t="str">
         <x:v>coryphaena hippurus</x:v>
       </x:c>
-      <x:c r="O17" s="62" t="n">
+      <x:c r="O17" s="32" t="n">
         <x:v>4.37</x:v>
       </x:c>
-      <x:c r="P17" s="46" t="str">
+      <x:c r="P17" s="24" t="str">
         <x:v>exact_2020_supplement</x:v>
       </x:c>
-      <x:c r="Q17" s="62" t="str">
+      <x:c r="Q17" s="32" t="str">
         <x:v>2020 supplement MeanTL</x:v>
       </x:c>
-      <x:c r="R17" s="46" t="str">
+      <x:c r="R17" s="24" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="S17" s="46" t="str">
+      <x:c r="S17" s="24" t="str">
         <x:v>Coryphaena hippurus</x:v>
       </x:c>
-      <x:c r="T17" s="62" t="n">
+      <x:c r="T17" s="32" t="n">
         <x:f>IF(O17="","",(1/'Metadata'!$B$5)^(O17-1))</x:f>
         <x:v>2344.228815319923</x:v>
       </x:c>
-      <x:c r="U17" s="60" t="n">
+      <x:c r="U17" s="31" t="n">
         <x:f>IF(T17="","",I17*T17)</x:f>
         <x:v>543480.6247674789</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="46" t="str">
-        <x:v>HS_081</x:v>
-      </x:c>
-      <x:c r="B18" s="46" t="str">
+      <x:c r="A18" s="24" t="str">
+        <x:v>HS_081</x:v>
+      </x:c>
+      <x:c r="B18" s="24" t="str">
         <x:v>Pacific, Southwest</x:v>
       </x:c>
-      <x:c r="C18" s="46" t="str">
+      <x:c r="C18" s="24" t="str">
         <x:v>High Seas</x:v>
       </x:c>
-      <x:c r="D18" s="58" t="n">
+      <x:c r="D18" s="30" t="n">
         <x:v>2019</x:v>
       </x:c>
-      <x:c r="E18" s="46" t="str">
+      <x:c r="E18" s="24" t="str">
         <x:v>Istiophoridae</x:v>
       </x:c>
-      <x:c r="F18" s="46" t="str">
+      <x:c r="F18" s="24" t="str">
         <x:v>Billfishes</x:v>
       </x:c>
-      <x:c r="G18" s="46" t="str">
+      <x:c r="G18" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="H18" s="46" t="str">
+      <x:c r="H18" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="I18" s="60" t="n">
+      <x:c r="I18" s="31" t="n">
         <x:v>144.3977809003</x:v>
       </x:c>
-      <x:c r="J18" s="60" t="n">
+      <x:c r="J18" s="31" t="n">
         <x:v>1.7973331205</x:v>
       </x:c>
-      <x:c r="K18" s="60" t="n">
+      <x:c r="K18" s="31" t="n">
         <x:v>142.6004477798</x:v>
       </x:c>
-      <x:c r="L18" s="60" t="n">
+      <x:c r="L18" s="31" t="n">
         <x:v>1.7973331205</x:v>
       </x:c>
-      <x:c r="M18" s="60" t="n">
+      <x:c r="M18" s="31" t="n">
         <x:v>142.6004477798</x:v>
       </x:c>
-      <x:c r="N18" s="46" t="str">
+      <x:c r="N18" s="24" t="str">
         <x:v>istiophoridae</x:v>
       </x:c>
-      <x:c r="O18" s="62" t="n">
+      <x:c r="O18" s="32" t="n">
         <x:v>4.48</x:v>
       </x:c>
-      <x:c r="P18" s="46" t="str">
+      <x:c r="P18" s="24" t="str">
         <x:v>exact_sea_around_us</x:v>
       </x:c>
-      <x:c r="Q18" s="62" t="str">
+      <x:c r="Q18" s="32" t="str">
         <x:v>Sea Around Us exploited organisms</x:v>
       </x:c>
-      <x:c r="R18" s="46" t="str">
+      <x:c r="R18" s="24" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="S18" s="46" t="str">
+      <x:c r="S18" s="24" t="str">
         <x:v>Istiophoridae</x:v>
       </x:c>
-      <x:c r="T18" s="62" t="n">
+      <x:c r="T18" s="32" t="n">
         <x:f>IF(O18="","",(1/'Metadata'!$B$5)^(O18-1))</x:f>
         <x:v>3019.951720402019</x:v>
       </x:c>
-      <x:c r="U18" s="60" t="n">
+      <x:c r="U18" s="31" t="n">
         <x:f>IF(T18="","",I18*T18)</x:f>
         <x:v>436074.3268520948</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="46" t="str">
-        <x:v>HS_081</x:v>
-      </x:c>
-      <x:c r="B19" s="46" t="str">
+      <x:c r="A19" s="24" t="str">
+        <x:v>HS_081</x:v>
+      </x:c>
+      <x:c r="B19" s="24" t="str">
         <x:v>Pacific, Southwest</x:v>
       </x:c>
-      <x:c r="C19" s="46" t="str">
+      <x:c r="C19" s="24" t="str">
         <x:v>High Seas</x:v>
       </x:c>
-      <x:c r="D19" s="58" t="n">
+      <x:c r="D19" s="30" t="n">
         <x:v>2019</x:v>
       </x:c>
-      <x:c r="E19" s="46" t="str">
+      <x:c r="E19" s="24" t="str">
         <x:v>Alopias</x:v>
       </x:c>
-      <x:c r="F19" s="46" t="str">
+      <x:c r="F19" s="24" t="str">
         <x:v>Thresher sharks</x:v>
       </x:c>
-      <x:c r="G19" s="46" t="str">
+      <x:c r="G19" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="H19" s="46" t="str">
+      <x:c r="H19" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="I19" s="60" t="n">
+      <x:c r="I19" s="31" t="n">
         <x:v>131.78268506930002</x:v>
       </x:c>
-      <x:c r="J19" s="60" t="n">
+      <x:c r="J19" s="31" t="n">
         <x:v>54.127921174600004</x:v>
       </x:c>
-      <x:c r="K19" s="60" t="n">
+      <x:c r="K19" s="31" t="n">
         <x:v>77.65476389470001</x:v>
       </x:c>
-      <x:c r="L19" s="60" t="n">
+      <x:c r="L19" s="31" t="n">
         <x:v>54.127921174600004</x:v>
       </x:c>
-      <x:c r="M19" s="60" t="n">
+      <x:c r="M19" s="31" t="n">
         <x:v>77.65476389470001</x:v>
       </x:c>
-      <x:c r="N19" s="46" t="str">
+      <x:c r="N19" s="24" t="str">
         <x:v>alopias</x:v>
       </x:c>
-      <x:c r="O19" s="62" t="n">
+      <x:c r="O19" s="32" t="n">
         <x:v>4.5</x:v>
       </x:c>
-      <x:c r="P19" s="46" t="str">
+      <x:c r="P19" s="24" t="str">
         <x:v>exact_sea_around_us</x:v>
       </x:c>
-      <x:c r="Q19" s="62" t="str">
+      <x:c r="Q19" s="32" t="str">
         <x:v>Sea Around Us exploited organisms</x:v>
       </x:c>
-      <x:c r="R19" s="46" t="str">
+      <x:c r="R19" s="24" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="S19" s="46" t="str">
+      <x:c r="S19" s="24" t="str">
         <x:v>Alopias</x:v>
       </x:c>
-      <x:c r="T19" s="62" t="n">
+      <x:c r="T19" s="32" t="n">
         <x:f>IF(O19="","",(1/'Metadata'!$B$5)^(O19-1))</x:f>
         <x:v>3162.2776601683795</x:v>
       </x:c>
-      <x:c r="U19" s="60" t="n">
+      <x:c r="U19" s="31" t="n">
         <x:f>IF(T19="","",I19*T19)</x:f>
         <x:v>416733.4409916525</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
-      <x:c r="A20" s="46" t="str">
-        <x:v>HS_081</x:v>
-      </x:c>
-      <x:c r="B20" s="46" t="str">
+      <x:c r="A20" s="24" t="str">
+        <x:v>HS_081</x:v>
+      </x:c>
+      <x:c r="B20" s="24" t="str">
         <x:v>Pacific, Southwest</x:v>
       </x:c>
-      <x:c r="C20" s="46" t="str">
+      <x:c r="C20" s="24" t="str">
         <x:v>High Seas</x:v>
       </x:c>
-      <x:c r="D20" s="58" t="n">
+      <x:c r="D20" s="30" t="n">
         <x:v>2019</x:v>
       </x:c>
-      <x:c r="E20" s="46" t="str">
+      <x:c r="E20" s="24" t="str">
         <x:v>Carcharhinus falciformis</x:v>
       </x:c>
-      <x:c r="F20" s="46" t="str">
+      <x:c r="F20" s="24" t="str">
         <x:v>Silky shark</x:v>
       </x:c>
-      <x:c r="G20" s="46" t="str">
+      <x:c r="G20" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="H20" s="46" t="str">
+      <x:c r="H20" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="I20" s="60" t="n">
+      <x:c r="I20" s="31" t="n">
         <x:v>129.4978770118</x:v>
       </x:c>
-      <x:c r="J20" s="60" t="n">
+      <x:c r="J20" s="31" t="n">
         <x:v>3.3006898047</x:v>
       </x:c>
-      <x:c r="K20" s="60" t="n">
+      <x:c r="K20" s="31" t="n">
         <x:v>126.1971872071</x:v>
       </x:c>
-      <x:c r="L20" s="60" t="n">
+      <x:c r="L20" s="31" t="n">
         <x:v>3.3006898047</x:v>
       </x:c>
-      <x:c r="M20" s="60" t="n">
+      <x:c r="M20" s="31" t="n">
         <x:v>126.1971872071</x:v>
       </x:c>
-      <x:c r="N20" s="46" t="str">
+      <x:c r="N20" s="24" t="str">
         <x:v>carcharhinus falciformis</x:v>
       </x:c>
-      <x:c r="O20" s="62" t="n">
+      <x:c r="O20" s="32" t="n">
         <x:v>4.51</x:v>
       </x:c>
-      <x:c r="P20" s="46" t="str">
+      <x:c r="P20" s="24" t="str">
         <x:v>exact_2020_supplement</x:v>
       </x:c>
-      <x:c r="Q20" s="62" t="str">
+      <x:c r="Q20" s="32" t="str">
         <x:v>2020 supplement MeanTL</x:v>
       </x:c>
-      <x:c r="R20" s="46" t="str">
+      <x:c r="R20" s="24" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="S20" s="46" t="str">
+      <x:c r="S20" s="24" t="str">
         <x:v>Carcharhinus falciformis</x:v>
       </x:c>
-      <x:c r="T20" s="62" t="n">
+      <x:c r="T20" s="32" t="n">
         <x:f>IF(O20="","",(1/'Metadata'!$B$5)^(O20-1))</x:f>
         <x:v>3235.936569296281</x:v>
       </x:c>
-      <x:c r="U20" s="60" t="n">
+      <x:c r="U20" s="31" t="n">
         <x:f>IF(T20="","",I20*T20)</x:f>
         <x:v>419046.91586871585</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
-      <x:c r="A21" s="46" t="str">
-        <x:v>HS_081</x:v>
-      </x:c>
-      <x:c r="B21" s="46" t="str">
+      <x:c r="A21" s="24" t="str">
+        <x:v>HS_081</x:v>
+      </x:c>
+      <x:c r="B21" s="24" t="str">
         <x:v>Pacific, Southwest</x:v>
       </x:c>
-      <x:c r="C21" s="46" t="str">
+      <x:c r="C21" s="24" t="str">
         <x:v>High Seas</x:v>
       </x:c>
-      <x:c r="D21" s="58" t="n">
+      <x:c r="D21" s="30" t="n">
         <x:v>2019</x:v>
       </x:c>
-      <x:c r="E21" s="46" t="str">
+      <x:c r="E21" s="24" t="str">
         <x:v>Lamna nasus</x:v>
       </x:c>
-      <x:c r="F21" s="46" t="str">
+      <x:c r="F21" s="24" t="str">
         <x:v>Porbeagle</x:v>
       </x:c>
-      <x:c r="G21" s="46" t="str">
+      <x:c r="G21" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="H21" s="46" t="str">
+      <x:c r="H21" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="I21" s="60" t="n">
+      <x:c r="I21" s="31" t="n">
         <x:v>65.8715912855</x:v>
       </x:c>
-      <x:c r="J21" s="60" t="n">
+      <x:c r="J21" s="31" t="n">
         <x:v>65.8715912855</x:v>
       </x:c>
-      <x:c r="K21" s="60" t="n">
+      <x:c r="K21" s="31" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L21" s="60" t="n">
+      <x:c r="L21" s="31" t="n">
         <x:v>65.8715912855</x:v>
       </x:c>
-      <x:c r="M21" s="60" t="n">
+      <x:c r="M21" s="31" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N21" s="46" t="str">
+      <x:c r="N21" s="24" t="str">
         <x:v>lamna nasus</x:v>
       </x:c>
-      <x:c r="O21" s="62" t="n">
+      <x:c r="O21" s="32" t="n">
         <x:v>4.57</x:v>
       </x:c>
-      <x:c r="P21" s="46" t="str">
+      <x:c r="P21" s="24" t="str">
         <x:v>exact_2020_supplement</x:v>
       </x:c>
-      <x:c r="Q21" s="62" t="str">
+      <x:c r="Q21" s="32" t="str">
         <x:v>2020 supplement MeanTL</x:v>
       </x:c>
-      <x:c r="R21" s="46" t="str">
+      <x:c r="R21" s="24" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="S21" s="46" t="str">
+      <x:c r="S21" s="24" t="str">
         <x:v>Lamna nasus</x:v>
       </x:c>
-      <x:c r="T21" s="62" t="n">
+      <x:c r="T21" s="32" t="n">
         <x:f>IF(O21="","",(1/'Metadata'!$B$5)^(O21-1))</x:f>
         <x:v>3715.3522909717276</x:v>
       </x:c>
-      <x:c r="U21" s="60" t="n">
+      <x:c r="U21" s="31" t="n">
         <x:f>IF(T21="","",I21*T21)</x:f>
         <x:v>244736.16759253573</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
-      <x:c r="A22" s="46" t="str">
-        <x:v>HS_081</x:v>
-      </x:c>
-      <x:c r="B22" s="46" t="str">
+      <x:c r="A22" s="24" t="str">
+        <x:v>HS_081</x:v>
+      </x:c>
+      <x:c r="B22" s="24" t="str">
         <x:v>Pacific, Southwest</x:v>
       </x:c>
-      <x:c r="C22" s="46" t="str">
+      <x:c r="C22" s="24" t="str">
         <x:v>High Seas</x:v>
       </x:c>
-      <x:c r="D22" s="58" t="n">
+      <x:c r="D22" s="30" t="n">
         <x:v>2019</x:v>
       </x:c>
-      <x:c r="E22" s="46" t="str">
+      <x:c r="E22" s="24" t="str">
         <x:v>Istiompax indica</x:v>
       </x:c>
-      <x:c r="F22" s="46" t="str">
+      <x:c r="F22" s="24" t="str">
         <x:v>Black marlin</x:v>
       </x:c>
-      <x:c r="G22" s="46" t="str">
+      <x:c r="G22" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="H22" s="46" t="str">
+      <x:c r="H22" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="I22" s="60" t="n">
+      <x:c r="I22" s="31" t="n">
         <x:v>59.107906649</x:v>
       </x:c>
-      <x:c r="J22" s="60" t="n">
+      <x:c r="J22" s="31" t="n">
         <x:v>59.107906649</x:v>
       </x:c>
-      <x:c r="K22" s="60" t="n">
+      <x:c r="K22" s="31" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L22" s="60" t="n">
+      <x:c r="L22" s="31" t="n">
         <x:v>59.107906649</x:v>
       </x:c>
-      <x:c r="M22" s="60" t="n">
+      <x:c r="M22" s="31" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N22" s="46" t="str">
+      <x:c r="N22" s="24" t="str">
         <x:v>istiompax indica</x:v>
       </x:c>
-      <x:c r="O22" s="62" t="n">
+      <x:c r="O22" s="32" t="n">
         <x:v>4.5</x:v>
       </x:c>
-      <x:c r="P22" s="46" t="str">
+      <x:c r="P22" s="24" t="str">
         <x:v>exact_2020_supplement</x:v>
       </x:c>
-      <x:c r="Q22" s="62" t="str">
+      <x:c r="Q22" s="32" t="str">
         <x:v>2020 supplement MeanTL</x:v>
       </x:c>
-      <x:c r="R22" s="46" t="str">
+      <x:c r="R22" s="24" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="S22" s="46" t="str">
+      <x:c r="S22" s="24" t="str">
         <x:v>Istiompax indica</x:v>
       </x:c>
-      <x:c r="T22" s="62" t="n">
+      <x:c r="T22" s="32" t="n">
         <x:f>IF(O22="","",(1/'Metadata'!$B$5)^(O22-1))</x:f>
         <x:v>3162.2776601683795</x:v>
       </x:c>
-      <x:c r="U22" s="60" t="n">
+      <x:c r="U22" s="31" t="n">
         <x:f>IF(T22="","",I22*T22)</x:f>
         <x:v>186915.61273545073</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
-      <x:c r="A23" s="46" t="str">
-        <x:v>HS_081</x:v>
-      </x:c>
-      <x:c r="B23" s="46" t="str">
+      <x:c r="A23" s="24" t="str">
+        <x:v>HS_081</x:v>
+      </x:c>
+      <x:c r="B23" s="24" t="str">
         <x:v>Pacific, Southwest</x:v>
       </x:c>
-      <x:c r="C23" s="46" t="str">
+      <x:c r="C23" s="24" t="str">
         <x:v>High Seas</x:v>
       </x:c>
-      <x:c r="D23" s="58" t="n">
+      <x:c r="D23" s="30" t="n">
         <x:v>2019</x:v>
       </x:c>
-      <x:c r="E23" s="46" t="str">
+      <x:c r="E23" s="24" t="str">
         <x:v>Sphyrna</x:v>
       </x:c>
-      <x:c r="F23" s="46" t="str">
+      <x:c r="F23" s="24" t="str">
         <x:v>Hammerhead sharks</x:v>
       </x:c>
-      <x:c r="G23" s="46" t="str">
+      <x:c r="G23" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="H23" s="46" t="str">
+      <x:c r="H23" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="I23" s="60" t="n">
+      <x:c r="I23" s="31" t="n">
         <x:v>28.168198206299998</x:v>
       </x:c>
-      <x:c r="J23" s="60" t="n">
+      <x:c r="J23" s="31" t="n">
         <x:v>28.168198206299998</x:v>
       </x:c>
-      <x:c r="K23" s="60" t="n">
+      <x:c r="K23" s="31" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L23" s="60" t="n">
+      <x:c r="L23" s="31" t="n">
         <x:v>28.168198206299998</x:v>
       </x:c>
-      <x:c r="M23" s="60" t="n">
+      <x:c r="M23" s="31" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N23" s="46" t="str">
+      <x:c r="N23" s="24" t="str">
         <x:v>sphyrna</x:v>
       </x:c>
-      <x:c r="O23" s="62" t="n">
+      <x:c r="O23" s="32" t="n">
         <x:v>4.2</x:v>
       </x:c>
-      <x:c r="P23" s="46" t="str">
+      <x:c r="P23" s="24" t="str">
         <x:v>exact_sea_around_us</x:v>
       </x:c>
-      <x:c r="Q23" s="62" t="str">
+      <x:c r="Q23" s="32" t="str">
         <x:v>Sea Around Us exploited organisms</x:v>
       </x:c>
-      <x:c r="R23" s="46" t="str">
+      <x:c r="R23" s="24" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="S23" s="46" t="str">
+      <x:c r="S23" s="24" t="str">
         <x:v>Sphyrna</x:v>
       </x:c>
-      <x:c r="T23" s="62" t="n">
+      <x:c r="T23" s="32" t="n">
         <x:f>IF(O23="","",(1/'Metadata'!$B$5)^(O23-1))</x:f>
         <x:v>1584.893192461114</x:v>
       </x:c>
-      <x:c r="U23" s="60" t="n">
+      <x:c r="U23" s="31" t="n">
         <x:f>IF(T23="","",I23*T23)</x:f>
         <x:v>44643.58558106023</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
-      <x:c r="A24" s="46" t="str">
-        <x:v>HS_081</x:v>
-      </x:c>
-      <x:c r="B24" s="46" t="str">
+      <x:c r="A24" s="24" t="str">
+        <x:v>HS_081</x:v>
+      </x:c>
+      <x:c r="B24" s="24" t="str">
         <x:v>Pacific, Southwest</x:v>
       </x:c>
-      <x:c r="C24" s="46" t="str">
+      <x:c r="C24" s="24" t="str">
         <x:v>High Seas</x:v>
       </x:c>
-      <x:c r="D24" s="58" t="n">
+      <x:c r="D24" s="30" t="n">
         <x:v>2019</x:v>
       </x:c>
-      <x:c r="E24" s="46" t="str">
+      <x:c r="E24" s="24" t="str">
         <x:v>Acanthocybium solandri</x:v>
       </x:c>
-      <x:c r="F24" s="46" t="str">
+      <x:c r="F24" s="24" t="str">
         <x:v>Wahoo</x:v>
       </x:c>
-      <x:c r="G24" s="46" t="str">
+      <x:c r="G24" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="H24" s="46" t="str">
+      <x:c r="H24" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="I24" s="60" t="n">
+      <x:c r="I24" s="31" t="n">
         <x:v>16.2771367694</x:v>
       </x:c>
-      <x:c r="J24" s="60" t="n">
+      <x:c r="J24" s="31" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K24" s="60" t="n">
+      <x:c r="K24" s="31" t="n">
         <x:v>16.2771367694</x:v>
       </x:c>
-      <x:c r="L24" s="60" t="n">
+      <x:c r="L24" s="31" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M24" s="60" t="n">
+      <x:c r="M24" s="31" t="n">
         <x:v>16.2771367694</x:v>
       </x:c>
-      <x:c r="N24" s="46" t="str">
+      <x:c r="N24" s="24" t="str">
         <x:v>acanthocybium solandri</x:v>
       </x:c>
-      <x:c r="O24" s="62" t="n">
+      <x:c r="O24" s="32" t="n">
         <x:v>4.26</x:v>
       </x:c>
-      <x:c r="P24" s="46" t="str">
+      <x:c r="P24" s="24" t="str">
         <x:v>exact_2020_supplement</x:v>
       </x:c>
-      <x:c r="Q24" s="62" t="str">
+      <x:c r="Q24" s="32" t="str">
         <x:v>2020 supplement MeanTL</x:v>
       </x:c>
-      <x:c r="R24" s="46" t="str">
+      <x:c r="R24" s="24" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="S24" s="46" t="str">
+      <x:c r="S24" s="24" t="str">
         <x:v>Acanthocybium solandri</x:v>
       </x:c>
-      <x:c r="T24" s="62" t="n">
+      <x:c r="T24" s="32" t="n">
         <x:f>IF(O24="","",(1/'Metadata'!$B$5)^(O24-1))</x:f>
         <x:v>1819.7008586099826</x:v>
       </x:c>
-      <x:c r="U24" s="60" t="n">
+      <x:c r="U24" s="31" t="n">
         <x:f>IF(T24="","",I24*T24)</x:f>
         <x:v>29619.519754989295</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="18" customHeight="1">
-      <x:c r="A25" s="46" t="str">
-        <x:v>HS_081</x:v>
-      </x:c>
-      <x:c r="B25" s="46" t="str">
+      <x:c r="A25" s="24" t="str">
+        <x:v>HS_081</x:v>
+      </x:c>
+      <x:c r="B25" s="24" t="str">
         <x:v>Pacific, Southwest</x:v>
       </x:c>
-      <x:c r="C25" s="46" t="str">
+      <x:c r="C25" s="24" t="str">
         <x:v>High Seas</x:v>
       </x:c>
-      <x:c r="D25" s="58" t="n">
+      <x:c r="D25" s="30" t="n">
         <x:v>2019</x:v>
       </x:c>
-      <x:c r="E25" s="46" t="str">
+      <x:c r="E25" s="24" t="str">
         <x:v>Coryphaena</x:v>
       </x:c>
-      <x:c r="F25" s="46" t="str">
+      <x:c r="F25" s="24" t="str">
         <x:v>Dolphinfishes</x:v>
       </x:c>
-      <x:c r="G25" s="46" t="str">
+      <x:c r="G25" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="H25" s="46" t="str">
+      <x:c r="H25" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="I25" s="60" t="n">
+      <x:c r="I25" s="31" t="n">
         <x:v>1.6313844051</x:v>
       </x:c>
-      <x:c r="J25" s="60" t="n">
+      <x:c r="J25" s="31" t="n">
         <x:v>1.6313844051</x:v>
       </x:c>
-      <x:c r="K25" s="60" t="n">
+      <x:c r="K25" s="31" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L25" s="60" t="n">
+      <x:c r="L25" s="31" t="n">
         <x:v>1.6313844051</x:v>
       </x:c>
-      <x:c r="M25" s="60" t="n">
+      <x:c r="M25" s="31" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N25" s="46" t="str">
+      <x:c r="N25" s="24" t="str">
         <x:v>coryphaena</x:v>
       </x:c>
-      <x:c r="O25" s="62" t="n">
+      <x:c r="O25" s="32" t="n">
         <x:v>4.49</x:v>
       </x:c>
-      <x:c r="P25" s="46" t="str">
+      <x:c r="P25" s="24" t="str">
         <x:v>exact_sea_around_us</x:v>
       </x:c>
-      <x:c r="Q25" s="62" t="str">
+      <x:c r="Q25" s="32" t="str">
         <x:v>Sea Around Us exploited organisms</x:v>
       </x:c>
-      <x:c r="R25" s="46" t="str">
+      <x:c r="R25" s="24" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="S25" s="46" t="str">
+      <x:c r="S25" s="24" t="str">
         <x:v>Coryphaena</x:v>
       </x:c>
-      <x:c r="T25" s="62" t="n">
+      <x:c r="T25" s="32" t="n">
         <x:f>IF(O25="","",(1/'Metadata'!$B$5)^(O25-1))</x:f>
         <x:v>3090.295432513592</x:v>
       </x:c>
-      <x:c r="U25" s="60" t="n">
+      <x:c r="U25" s="31" t="n">
         <x:f>IF(T25="","",I25*T25)</x:f>
         <x:v>5041.459775754433</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="18" customHeight="1">
-      <x:c r="A26" s="46" t="str">
-        <x:v>HS_081</x:v>
-      </x:c>
-      <x:c r="B26" s="46" t="str">
+      <x:c r="A26" s="24" t="str">
+        <x:v>HS_081</x:v>
+      </x:c>
+      <x:c r="B26" s="24" t="str">
         <x:v>Pacific, Southwest</x:v>
       </x:c>
-      <x:c r="C26" s="46" t="str">
+      <x:c r="C26" s="24" t="str">
         <x:v>High Seas</x:v>
       </x:c>
-      <x:c r="D26" s="58" t="n">
+      <x:c r="D26" s="30" t="n">
         <x:v>2019</x:v>
       </x:c>
-      <x:c r="E26" s="46" t="str">
+      <x:c r="E26" s="24" t="str">
         <x:v>Tetrapturus angustirostris</x:v>
       </x:c>
-      <x:c r="F26" s="46" t="str">
+      <x:c r="F26" s="24" t="str">
         <x:v>Shortbill spearfish</x:v>
       </x:c>
-      <x:c r="G26" s="46" t="str">
+      <x:c r="G26" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="H26" s="46" t="str">
+      <x:c r="H26" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="I26" s="60" t="n">
+      <x:c r="I26" s="31" t="n">
         <x:v>1.5104209908</x:v>
       </x:c>
-      <x:c r="J26" s="60" t="n">
+      <x:c r="J26" s="31" t="n">
         <x:v>1.5104209908</x:v>
       </x:c>
-      <x:c r="K26" s="60" t="n">
+      <x:c r="K26" s="31" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L26" s="60" t="n">
+      <x:c r="L26" s="31" t="n">
         <x:v>1.5104209908</x:v>
       </x:c>
-      <x:c r="M26" s="60" t="n">
+      <x:c r="M26" s="31" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N26" s="46" t="str">
+      <x:c r="N26" s="24" t="str">
         <x:v>tetrapturus angustirostris</x:v>
       </x:c>
-      <x:c r="O26" s="62" t="n">
+      <x:c r="O26" s="32" t="n">
         <x:v>4.5</x:v>
       </x:c>
-      <x:c r="P26" s="46" t="str">
+      <x:c r="P26" s="24" t="str">
         <x:v>exact_2020_supplement</x:v>
       </x:c>
-      <x:c r="Q26" s="62" t="str">
+      <x:c r="Q26" s="32" t="str">
         <x:v>2020 supplement MeanTL</x:v>
       </x:c>
-      <x:c r="R26" s="46" t="str">
+      <x:c r="R26" s="24" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="S26" s="46" t="str">
+      <x:c r="S26" s="24" t="str">
         <x:v>Tetrapturus angustirostris</x:v>
       </x:c>
-      <x:c r="T26" s="62" t="n">
+      <x:c r="T26" s="32" t="n">
         <x:f>IF(O26="","",(1/'Metadata'!$B$5)^(O26-1))</x:f>
         <x:v>3162.2776601683795</x:v>
       </x:c>
-      <x:c r="U26" s="60" t="n">
+      <x:c r="U26" s="31" t="n">
         <x:f>IF(T26="","",I26*T26)</x:f>
         <x:v>4776.370556656229</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="18" customHeight="1">
-      <x:c r="A27" s="46" t="str">
-        <x:v>HS_081</x:v>
-      </x:c>
-      <x:c r="B27" s="46" t="str">
+      <x:c r="A27" s="24" t="str">
+        <x:v>HS_081</x:v>
+      </x:c>
+      <x:c r="B27" s="24" t="str">
         <x:v>Pacific, Southwest</x:v>
       </x:c>
-      <x:c r="C27" s="46" t="str">
+      <x:c r="C27" s="24" t="str">
         <x:v>High Seas</x:v>
       </x:c>
-      <x:c r="D27" s="58" t="n">
+      <x:c r="D27" s="30" t="n">
         <x:v>2019</x:v>
       </x:c>
-      <x:c r="E27" s="46" t="str">
+      <x:c r="E27" s="24" t="str">
         <x:v>Carangidae</x:v>
       </x:c>
-      <x:c r="F27" s="46" t="str">
+      <x:c r="F27" s="24" t="str">
         <x:v>Jacks, pompanos</x:v>
       </x:c>
-      <x:c r="G27" s="46" t="str">
+      <x:c r="G27" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="H27" s="46" t="str">
+      <x:c r="H27" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="I27" s="60" t="n">
+      <x:c r="I27" s="31" t="n">
         <x:v>0.6869070939</x:v>
       </x:c>
-      <x:c r="J27" s="60" t="n">
+      <x:c r="J27" s="31" t="n">
         <x:v>0.007982956400000001</x:v>
       </x:c>
-      <x:c r="K27" s="60" t="n">
+      <x:c r="K27" s="31" t="n">
         <x:v>0.6789241375</x:v>
       </x:c>
-      <x:c r="L27" s="60" t="n">
+      <x:c r="L27" s="31" t="n">
         <x:v>0.007982956400000001</x:v>
       </x:c>
-      <x:c r="M27" s="60" t="n">
+      <x:c r="M27" s="31" t="n">
         <x:v>0.6789241375</x:v>
       </x:c>
-      <x:c r="N27" s="46" t="str">
+      <x:c r="N27" s="24" t="str">
         <x:v>carangidae</x:v>
       </x:c>
-      <x:c r="O27" s="62" t="n">
+      <x:c r="O27" s="32" t="n">
         <x:v>4.05</x:v>
       </x:c>
-      <x:c r="P27" s="46" t="str">
+      <x:c r="P27" s="24" t="str">
         <x:v>exact_sea_around_us</x:v>
       </x:c>
-      <x:c r="Q27" s="62" t="str">
+      <x:c r="Q27" s="32" t="str">
         <x:v>Sea Around Us exploited organisms</x:v>
       </x:c>
-      <x:c r="R27" s="46" t="str">
+      <x:c r="R27" s="24" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="S27" s="46" t="str">
+      <x:c r="S27" s="24" t="str">
         <x:v>Carangidae</x:v>
       </x:c>
-      <x:c r="T27" s="62" t="n">
+      <x:c r="T27" s="32" t="n">
         <x:f>IF(O27="","",(1/'Metadata'!$B$5)^(O27-1))</x:f>
         <x:v>1122.018454301963</x:v>
       </x:c>
-      <x:c r="U27" s="60" t="n">
+      <x:c r="U27" s="31" t="n">
         <x:f>IF(T27="","",I27*T27)</x:f>
         <x:v>770.7224357467313</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="18" customHeight="1">
-      <x:c r="A28" s="46" t="str">
-        <x:v>HS_081</x:v>
-      </x:c>
-      <x:c r="B28" s="46" t="str">
+      <x:c r="A28" s="24" t="str">
+        <x:v>HS_081</x:v>
+      </x:c>
+      <x:c r="B28" s="24" t="str">
         <x:v>Pacific, Southwest</x:v>
       </x:c>
-      <x:c r="C28" s="46" t="str">
+      <x:c r="C28" s="24" t="str">
         <x:v>High Seas</x:v>
       </x:c>
-      <x:c r="D28" s="58" t="n">
+      <x:c r="D28" s="30" t="n">
         <x:v>2019</x:v>
       </x:c>
-      <x:c r="E28" s="46" t="str">
+      <x:c r="E28" s="24" t="str">
         <x:v>Istiophorus platypterus</x:v>
       </x:c>
-      <x:c r="F28" s="46" t="str">
+      <x:c r="F28" s="24" t="str">
         <x:v>Indo-Pacific sailfish</x:v>
       </x:c>
-      <x:c r="G28" s="46" t="str">
+      <x:c r="G28" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="H28" s="46" t="str">
+      <x:c r="H28" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="I28" s="60" t="n">
+      <x:c r="I28" s="31" t="n">
         <x:v>0.3172439163</x:v>
       </x:c>
-      <x:c r="J28" s="60" t="n">
+      <x:c r="J28" s="31" t="n">
         <x:v>0.3172439163</x:v>
       </x:c>
-      <x:c r="K28" s="60" t="n">
+      <x:c r="K28" s="31" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L28" s="60" t="n">
+      <x:c r="L28" s="31" t="n">
         <x:v>0.3172439163</x:v>
       </x:c>
-      <x:c r="M28" s="60" t="n">
+      <x:c r="M28" s="31" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N28" s="46" t="str">
+      <x:c r="N28" s="24" t="str">
         <x:v>istiophorus platypterus</x:v>
       </x:c>
-      <x:c r="O28" s="62" t="n">
+      <x:c r="O28" s="32" t="n">
         <x:v>4.5</x:v>
       </x:c>
-      <x:c r="P28" s="46" t="str">
+      <x:c r="P28" s="24" t="str">
         <x:v>exact_2020_supplement</x:v>
       </x:c>
-      <x:c r="Q28" s="62" t="str">
+      <x:c r="Q28" s="32" t="str">
         <x:v>2020 supplement MeanTL</x:v>
       </x:c>
-      <x:c r="R28" s="46" t="str">
+      <x:c r="R28" s="24" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="S28" s="46" t="str">
+      <x:c r="S28" s="24" t="str">
         <x:v>Istiophorus platypterus</x:v>
       </x:c>
-      <x:c r="T28" s="62" t="n">
+      <x:c r="T28" s="32" t="n">
         <x:f>IF(O28="","",(1/'Metadata'!$B$5)^(O28-1))</x:f>
         <x:v>3162.2776601683795</x:v>
       </x:c>
-      <x:c r="U28" s="60" t="n">
+      <x:c r="U28" s="31" t="n">
         <x:f>IF(T28="","",I28*T28)</x:f>
         <x:v>1003.2133493398172</x:v>
       </x:c>
@@ -2622,7 +2457,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd68163a878334fba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R283f53a962944838"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2632,303 +2467,109 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="56" t="str">
+      <x:c r="A1" s="29" t="str">
         <x:v>commercial_group</x:v>
       </x:c>
-      <x:c r="B1" s="56" t="str">
-        <x:v>taxon_count_total</x:v>
-      </x:c>
-      <x:c r="C1" s="56" t="str">
-        <x:v>taxon_count_matched</x:v>
-      </x:c>
-      <x:c r="D1" s="56" t="str">
-        <x:v>catch_tonnes_total</x:v>
-      </x:c>
-      <x:c r="E1" s="56" t="str">
+      <x:c r="B1" s="29" t="str">
         <x:v>catch_tonnes_matched</x:v>
       </x:c>
-      <x:c r="F1" s="56" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="56" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="56" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="56" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="56" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="56" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="56" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="56" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="56" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="56" t="str">
-        <x:v>jensen_percent_difference</x:v>
+      <x:c r="C1" s="29" t="str">
+        <x:v>tl_weighted</x:v>
+      </x:c>
+      <x:c r="D1" s="29" t="str">
+        <x:v>sppr</x:v>
+      </x:c>
+      <x:c r="E1" s="29" t="str">
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
-      <x:c r="A2" s="46" t="str">
+      <x:c r="A2" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B2" s="64" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="64" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="60" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>3492.4651876564</x:v>
       </x:c>
-      <x:c r="E2" s="60" t="n">
-        <x:v>3492.4651876564</x:v>
-      </x:c>
-      <x:c r="F2" s="62" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="66" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="62" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>200.6887637976973</x:v>
-      </x:c>
-      <x:c r="I2" s="60" t="n">
-        <x:f>SUMIF('Species'!$H$2:$H$28,A2,'Species'!$U$2:$U$28)</x:f>
-        <x:v>700898.5211172558</x:v>
-      </x:c>
-      <x:c r="J2" s="62" t="n">
+      <x:c r="C2" s="32" t="n">
         <x:v>3.301304313269694</x:v>
       </x:c>
-      <x:c r="K2" s="62" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
         <x:v>200.12636783119578</x:v>
       </x:c>
-      <x:c r="L2" s="60" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+      <x:c r="E2" s="31" t="n">
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>698934.3727825709</x:v>
       </x:c>
-      <x:c r="M2" s="60" t="n">
-        <x:f>I2-L2</x:f>
-        <x:v>1964.1483346848981</x:v>
-      </x:c>
-      <x:c r="N2" s="62" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0028102042354352</x:v>
-      </x:c>
-      <x:c r="O2" s="66" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.002810204235435304</x:v>
-      </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
-      <x:c r="A3" s="46" t="str">
+      <x:c r="A3" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B3" s="64" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C3" s="64" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D3" s="60" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>900.4425892744001</x:v>
       </x:c>
-      <x:c r="E3" s="60" t="n">
-        <x:v>900.4425892744001</x:v>
-      </x:c>
-      <x:c r="F3" s="62" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="66" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="62" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1956.5212883585396</x:v>
-      </x:c>
-      <x:c r="I3" s="60" t="n">
-        <x:f>SUMIF('Species'!$H$2:$H$28,A3,'Species'!$U$2:$U$28)</x:f>
-        <x:v>1761735.0948600485</x:v>
-      </x:c>
-      <x:c r="J3" s="62" t="n">
+      <x:c r="C3" s="32" t="n">
         <x:v>4.288578296498873</x:v>
       </x:c>
-      <x:c r="K3" s="62" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
         <x:v>1943.4720378418215</x:v>
       </x:c>
-      <x:c r="L3" s="60" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+      <x:c r="E3" s="31" t="n">
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>1749984.9939366847</x:v>
       </x:c>
-      <x:c r="M3" s="60" t="n">
-        <x:f>I3-L3</x:f>
-        <x:v>11750.100923363818</x:v>
-      </x:c>
-      <x:c r="N3" s="62" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0067144009600513</x:v>
-      </x:c>
-      <x:c r="O3" s="66" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.006714400960051285</x:v>
-      </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
-      <x:c r="A4" s="46" t="str">
+      <x:c r="A4" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B4" s="64" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C4" s="64" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D4" s="60" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>13144.3799647761</x:v>
       </x:c>
-      <x:c r="E4" s="60" t="n">
-        <x:v>13144.3799647761</x:v>
-      </x:c>
-      <x:c r="F4" s="62" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="66" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="62" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2196.2300994140164</x:v>
-      </x:c>
-      <x:c r="I4" s="60" t="n">
-        <x:f>SUMIF('Species'!$H$2:$H$28,A4,'Species'!$U$2:$U$28)</x:f>
-        <x:v>28868082.91677582</x:v>
-      </x:c>
-      <x:c r="J4" s="62" t="n">
+      <x:c r="C4" s="32" t="n">
         <x:v>4.329759704970958</x:v>
       </x:c>
-      <x:c r="K4" s="62" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
         <x:v>2136.779482806935</x:v>
       </x:c>
-      <x:c r="L4" s="60" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+      <x:c r="E4" s="31" t="n">
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>28086641.422952116</x:v>
       </x:c>
-      <x:c r="M4" s="60" t="n">
-        <x:f>I4-L4</x:f>
-        <x:v>781441.4938237034</x:v>
-      </x:c>
-      <x:c r="N4" s="62" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0278225325006327</x:v>
-      </x:c>
-      <x:c r="O4" s="66" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.02782253250063275</x:v>
-      </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
-      <x:c r="A5" s="46" t="str">
+      <x:c r="A5" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B5" s="64" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C5" s="64" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D5" s="60" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>27715.179081010196</x:v>
       </x:c>
-      <x:c r="E5" s="60" t="n">
-        <x:v>27715.179081010196</x:v>
-      </x:c>
-      <x:c r="F5" s="62" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="66" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="62" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2166.8837052932663</x:v>
-      </x:c>
-      <x:c r="I5" s="60" t="n">
-        <x:f>SUMIF('Species'!$H$2:$H$28,A5,'Species'!$U$2:$U$28)</x:f>
-        <x:v>60055569.9399258</x:v>
-      </x:c>
-      <x:c r="J5" s="62" t="n">
+      <x:c r="C5" s="32" t="n">
         <x:v>4.3123912418989345</x:v>
       </x:c>
-      <x:c r="K5" s="62" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
         <x:v>2053.010837285082</x:v>
       </x:c>
-      <x:c r="L5" s="60" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+      <x:c r="E5" s="31" t="n">
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>56899563.01061073</x:v>
       </x:c>
-      <x:c r="M5" s="60" t="n">
-        <x:f>I5-L5</x:f>
-        <x:v>3156006.929315068</x:v>
-      </x:c>
-      <x:c r="N5" s="62" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0554662771087808</x:v>
-      </x:c>
-      <x:c r="O5" s="66" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.055466277108780784</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G5">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O5">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf040280b47f6490f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9793875b2be54564"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2938,303 +2579,109 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="56" t="str">
+      <x:c r="A1" s="29" t="str">
         <x:v>functional_group</x:v>
       </x:c>
-      <x:c r="B1" s="56" t="str">
-        <x:v>taxon_count_total</x:v>
-      </x:c>
-      <x:c r="C1" s="56" t="str">
-        <x:v>taxon_count_matched</x:v>
-      </x:c>
-      <x:c r="D1" s="56" t="str">
-        <x:v>catch_tonnes_total</x:v>
-      </x:c>
-      <x:c r="E1" s="56" t="str">
+      <x:c r="B1" s="29" t="str">
         <x:v>catch_tonnes_matched</x:v>
       </x:c>
-      <x:c r="F1" s="56" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="56" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="56" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="56" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="56" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="56" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="56" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="56" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="56" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="56" t="str">
-        <x:v>jensen_percent_difference</x:v>
+      <x:c r="C1" s="29" t="str">
+        <x:v>tl_weighted</x:v>
+      </x:c>
+      <x:c r="D1" s="29" t="str">
+        <x:v>sppr</x:v>
+      </x:c>
+      <x:c r="E1" s="29" t="str">
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
-      <x:c r="A2" s="46" t="str">
+      <x:c r="A2" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B2" s="64" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C2" s="64" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D2" s="60" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>27964.925305575995</x:v>
       </x:c>
-      <x:c r="E2" s="60" t="n">
-        <x:v>27964.925305575995</x:v>
-      </x:c>
-      <x:c r="F2" s="62" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="66" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="62" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>2168.205739213404</x:v>
-      </x:c>
-      <x:c r="I2" s="60" t="n">
-        <x:f>SUMIF('Species'!$G$2:$G$28,A2,'Species'!$U$2:$U$28)</x:f>
-        <x:v>60633711.544224024</x:v>
-      </x:c>
-      <x:c r="J2" s="62" t="n">
+      <x:c r="C2" s="32" t="n">
         <x:v>4.312848702477923</x:v>
       </x:c>
-      <x:c r="K2" s="62" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
         <x:v>2055.1744989790063</x:v>
       </x:c>
-      <x:c r="L2" s="60" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+      <x:c r="E2" s="31" t="n">
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>57472801.35387248</x:v>
       </x:c>
-      <x:c r="M2" s="60" t="n">
-        <x:f>I2-L2</x:f>
-        <x:v>3160910.190351546</x:v>
-      </x:c>
-      <x:c r="N2" s="62" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0549983664601477</x:v>
-      </x:c>
-      <x:c r="O2" s="66" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.0549983664601476</x:v>
-      </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
-      <x:c r="A3" s="46" t="str">
+      <x:c r="A3" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="64" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C3" s="64" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D3" s="60" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>13144.3799647761</x:v>
       </x:c>
-      <x:c r="E3" s="60" t="n">
-        <x:v>13144.3799647761</x:v>
-      </x:c>
-      <x:c r="F3" s="62" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="66" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="62" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2196.2300994140164</x:v>
-      </x:c>
-      <x:c r="I3" s="60" t="n">
-        <x:f>SUMIF('Species'!$G$2:$G$28,A3,'Species'!$U$2:$U$28)</x:f>
-        <x:v>28868082.91677582</x:v>
-      </x:c>
-      <x:c r="J3" s="62" t="n">
+      <x:c r="C3" s="32" t="n">
         <x:v>4.329759704970958</x:v>
       </x:c>
-      <x:c r="K3" s="62" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
         <x:v>2136.779482806935</x:v>
       </x:c>
-      <x:c r="L3" s="60" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+      <x:c r="E3" s="31" t="n">
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>28086641.422952116</x:v>
       </x:c>
-      <x:c r="M3" s="60" t="n">
-        <x:f>I3-L3</x:f>
-        <x:v>781441.4938237034</x:v>
-      </x:c>
-      <x:c r="N3" s="62" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0278225325006327</x:v>
-      </x:c>
-      <x:c r="O3" s="66" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.02782253250063275</x:v>
-      </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
-      <x:c r="A4" s="46" t="str">
+      <x:c r="A4" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="64" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="64" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="60" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>2429.5427242088</x:v>
       </x:c>
-      <x:c r="E4" s="60" t="n">
-        <x:v>2429.5427242088</x:v>
-      </x:c>
-      <x:c r="F4" s="62" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="66" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="62" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.28</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
         <x:v>190.54607179632464</x:v>
       </x:c>
-      <x:c r="I4" s="60" t="n">
-        <x:f>SUMIF('Species'!$G$2:$G$28,A4,'Species'!$U$2:$U$28)</x:f>
+      <x:c r="E4" s="31" t="n">
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>462939.82235932816</x:v>
       </x:c>
-      <x:c r="J4" s="62" t="n">
-        <x:v>3.28</x:v>
-      </x:c>
-      <x:c r="K4" s="62" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>190.54607179632464</x:v>
-      </x:c>
-      <x:c r="L4" s="60" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>462939.82235932816</x:v>
-      </x:c>
-      <x:c r="M4" s="60" t="n">
-        <x:f>I4-L4</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="62" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="66" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
-      <x:c r="A5" s="46" t="str">
+      <x:c r="A5" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="64" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C5" s="64" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D5" s="60" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>1713.6188281562</x:v>
       </x:c>
-      <x:c r="E5" s="60" t="n">
-        <x:v>1713.6188281562</x:v>
-      </x:c>
-      <x:c r="F5" s="62" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="66" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="62" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>829.5614905499718</x:v>
-      </x:c>
-      <x:c r="I5" s="60" t="n">
-        <x:f>SUMIF('Species'!$G$2:$G$28,A5,'Species'!$U$2:$U$28)</x:f>
-        <x:v>1421552.1893197533</x:v>
-      </x:c>
-      <x:c r="J5" s="62" t="n">
+      <x:c r="C5" s="32" t="n">
         <x:v>3.69546156453712</x:v>
       </x:c>
-      <x:c r="K5" s="62" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
         <x:v>495.9770310281046</x:v>
       </x:c>
-      <x:c r="L5" s="60" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+      <x:c r="E5" s="31" t="n">
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>849915.5787027718</x:v>
       </x:c>
-      <x:c r="M5" s="60" t="n">
-        <x:f>I5-L5</x:f>
-        <x:v>571636.6106169815</x:v>
-      </x:c>
-      <x:c r="N5" s="62" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.6725804596845628</x:v>
-      </x:c>
-      <x:c r="O5" s="66" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.6725804596845628</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G5">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O5">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb77a46bb5a564de5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R507824525509483f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3267,67 +2714,67 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="56" t="str">
+      <x:c r="A1" s="29" t="str">
         <x:v>unit_id</x:v>
       </x:c>
-      <x:c r="B1" s="56" t="str">
+      <x:c r="B1" s="29" t="str">
         <x:v>region_name</x:v>
       </x:c>
-      <x:c r="C1" s="56" t="str">
+      <x:c r="C1" s="29" t="str">
         <x:v>region_type</x:v>
       </x:c>
-      <x:c r="D1" s="56" t="str">
+      <x:c r="D1" s="29" t="str">
         <x:v>year</x:v>
       </x:c>
-      <x:c r="E1" s="56" t="str">
+      <x:c r="E1" s="29" t="str">
         <x:v>taxon</x:v>
       </x:c>
-      <x:c r="F1" s="56" t="str">
+      <x:c r="F1" s="29" t="str">
         <x:v>common_name</x:v>
       </x:c>
-      <x:c r="G1" s="56" t="str">
+      <x:c r="G1" s="29" t="str">
         <x:v>functional_group</x:v>
       </x:c>
-      <x:c r="H1" s="56" t="str">
+      <x:c r="H1" s="29" t="str">
         <x:v>commercial_group</x:v>
       </x:c>
-      <x:c r="I1" s="56" t="str">
+      <x:c r="I1" s="29" t="str">
         <x:v>catch_tonnes</x:v>
       </x:c>
-      <x:c r="J1" s="56" t="str">
+      <x:c r="J1" s="29" t="str">
         <x:v>landings_tonnes</x:v>
       </x:c>
-      <x:c r="K1" s="56" t="str">
+      <x:c r="K1" s="29" t="str">
         <x:v>discards_tonnes</x:v>
       </x:c>
-      <x:c r="L1" s="56" t="str">
+      <x:c r="L1" s="29" t="str">
         <x:v>reported_tonnes</x:v>
       </x:c>
-      <x:c r="M1" s="56" t="str">
+      <x:c r="M1" s="29" t="str">
         <x:v>unreported_tonnes</x:v>
       </x:c>
-      <x:c r="N1" s="56" t="str">
+      <x:c r="N1" s="29" t="str">
         <x:v>taxon_key</x:v>
       </x:c>
-      <x:c r="O1" s="56" t="str">
+      <x:c r="O1" s="29" t="str">
         <x:v>tl</x:v>
       </x:c>
-      <x:c r="P1" s="56" t="str">
+      <x:c r="P1" s="29" t="str">
         <x:v>match_method</x:v>
       </x:c>
-      <x:c r="Q1" s="56" t="str">
+      <x:c r="Q1" s="29" t="str">
         <x:v>tl_source</x:v>
       </x:c>
-      <x:c r="R1" s="56" t="str">
+      <x:c r="R1" s="29" t="str">
         <x:v>match_confidence</x:v>
       </x:c>
-      <x:c r="S1" s="56" t="str">
+      <x:c r="S1" s="29" t="str">
         <x:v>reference_taxon</x:v>
       </x:c>
-      <x:c r="T1" s="56" t="str">
+      <x:c r="T1" s="29" t="str">
         <x:v>sppr</x:v>
       </x:c>
-      <x:c r="U1" s="56" t="str">
+      <x:c r="U1" s="29" t="str">
         <x:v>ppr</x:v>
       </x:c>
     </x:row>
@@ -3347,275 +2794,247 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="56" t="str">
+      <x:c r="A1" s="29" t="str">
         <x:v>unit_id</x:v>
       </x:c>
-      <x:c r="B1" s="56" t="str">
+      <x:c r="B1" s="29" t="str">
         <x:v>check</x:v>
       </x:c>
-      <x:c r="C1" s="56" t="str">
+      <x:c r="C1" s="29" t="str">
         <x:v>value</x:v>
       </x:c>
-      <x:c r="D1" s="56" t="str">
+      <x:c r="D1" s="29" t="str">
         <x:v>unit</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
-      <x:c r="A2" s="46" t="str">
-        <x:v>HS_081</x:v>
-      </x:c>
-      <x:c r="B2" s="46" t="str">
+      <x:c r="A2" s="24" t="str">
+        <x:v>HS_081</x:v>
+      </x:c>
+      <x:c r="B2" s="24" t="str">
         <x:v>raw_filtered_tonnes</x:v>
       </x:c>
-      <x:c r="C2" s="46" t="n">
+      <x:c r="C2" s="24" t="n">
         <x:v>45252.4668227171</x:v>
       </x:c>
-      <x:c r="D2" s="46" t="str">
+      <x:c r="D2" s="24" t="str">
         <x:v>tonnes</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
-      <x:c r="A3" s="46" t="str">
-        <x:v>HS_081</x:v>
-      </x:c>
-      <x:c r="B3" s="46" t="str">
+      <x:c r="A3" s="24" t="str">
+        <x:v>HS_081</x:v>
+      </x:c>
+      <x:c r="B3" s="24" t="str">
         <x:v>species_catch_tonnes</x:v>
       </x:c>
-      <x:c r="C3" s="46" t="n">
+      <x:c r="C3" s="24" t="n">
         <x:v>45252.466822717106</x:v>
       </x:c>
-      <x:c r="D3" s="46" t="str">
+      <x:c r="D3" s="24" t="str">
         <x:v>tonnes</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
-      <x:c r="A4" s="46" t="str">
-        <x:v>HS_081</x:v>
-      </x:c>
-      <x:c r="B4" s="46" t="str">
+      <x:c r="A4" s="24" t="str">
+        <x:v>HS_081</x:v>
+      </x:c>
+      <x:c r="B4" s="24" t="str">
         <x:v>catch_difference_tonnes</x:v>
       </x:c>
-      <x:c r="C4" s="46" t="n">
+      <x:c r="C4" s="24" t="n">
         <x:v>7.275957614183426e-12</x:v>
       </x:c>
-      <x:c r="D4" s="46" t="str">
+      <x:c r="D4" s="24" t="str">
         <x:v>tonnes</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
-      <x:c r="A5" s="46" t="str">
-        <x:v>HS_081</x:v>
-      </x:c>
-      <x:c r="B5" s="46" t="str">
+      <x:c r="A5" s="24" t="str">
+        <x:v>HS_081</x:v>
+      </x:c>
+      <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="46" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="D5" s="46" t="str">
+      <x:c r="C5" s="33" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D5" s="24" t="str">
         <x:v>boolean</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
-      <x:c r="A6" s="46" t="str">
-        <x:v>HS_081</x:v>
-      </x:c>
-      <x:c r="B6" s="46" t="str">
+      <x:c r="A6" s="24" t="str">
+        <x:v>HS_081</x:v>
+      </x:c>
+      <x:c r="B6" s="24" t="str">
         <x:v>matched_catch_tonnes</x:v>
       </x:c>
-      <x:c r="C6" s="46" t="n">
+      <x:c r="C6" s="24" t="n">
         <x:v>45252.466822717106</x:v>
       </x:c>
-      <x:c r="D6" s="46" t="str">
+      <x:c r="D6" s="24" t="str">
         <x:v>tonnes</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
-      <x:c r="A7" s="46" t="str">
-        <x:v>HS_081</x:v>
-      </x:c>
-      <x:c r="B7" s="46" t="str">
+      <x:c r="A7" s="24" t="str">
+        <x:v>HS_081</x:v>
+      </x:c>
+      <x:c r="B7" s="24" t="str">
         <x:v>catch_coverage_fraction</x:v>
       </x:c>
-      <x:c r="C7" s="46" t="n">
+      <x:c r="C7" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D7" s="46" t="str">
+      <x:c r="D7" s="24" t="str">
         <x:v>fraction</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
-      <x:c r="A8" s="46" t="str">
-        <x:v>HS_081</x:v>
-      </x:c>
-      <x:c r="B8" s="46" t="str">
+      <x:c r="A8" s="24" t="str">
+        <x:v>HS_081</x:v>
+      </x:c>
+      <x:c r="B8" s="24" t="str">
         <x:v>taxa_count</x:v>
       </x:c>
-      <x:c r="C8" s="46" t="n">
+      <x:c r="C8" s="24" t="n">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="D8" s="46" t="str">
+      <x:c r="D8" s="24" t="str">
         <x:v>count</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
-      <x:c r="A9" s="46" t="str">
-        <x:v>HS_081</x:v>
-      </x:c>
-      <x:c r="B9" s="46" t="str">
+      <x:c r="A9" s="24" t="str">
+        <x:v>HS_081</x:v>
+      </x:c>
+      <x:c r="B9" s="24" t="str">
         <x:v>matched_taxa_count</x:v>
       </x:c>
-      <x:c r="C9" s="46" t="n">
+      <x:c r="C9" s="24" t="n">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="D9" s="46" t="str">
+      <x:c r="D9" s="24" t="str">
         <x:v>count</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
-      <x:c r="A10" s="46" t="str">
-        <x:v>HS_081</x:v>
-      </x:c>
-      <x:c r="B10" s="46" t="str">
+      <x:c r="A10" s="24" t="str">
+        <x:v>HS_081</x:v>
+      </x:c>
+      <x:c r="B10" s="24" t="str">
         <x:v>unmatched_taxa_count</x:v>
       </x:c>
-      <x:c r="C10" s="46" t="n">
+      <x:c r="C10" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D10" s="46" t="str">
+      <x:c r="D10" s="24" t="str">
         <x:v>count</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
-      <x:c r="A11" s="46" t="str">
-        <x:v>HS_081</x:v>
-      </x:c>
-      <x:c r="B11" s="46" t="str">
+      <x:c r="A11" s="24" t="str">
+        <x:v>HS_081</x:v>
+      </x:c>
+      <x:c r="B11" s="24" t="str">
         <x:v>species_ppr</x:v>
       </x:c>
-      <x:c r="C11" s="46" t="n">
+      <x:c r="C11" s="24" t="n">
         <x:v>91386286.47267893</x:v>
       </x:c>
-      <x:c r="D11" s="46" t="str">
+      <x:c r="D11" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
-      <x:c r="A12" s="46" t="str">
-        <x:v>HS_081</x:v>
-      </x:c>
-      <x:c r="B12" s="46" t="str">
+      <x:c r="A12" s="24" t="str">
+        <x:v>HS_081</x:v>
+      </x:c>
+      <x:c r="B12" s="24" t="str">
         <x:v>commercial_ppr</x:v>
       </x:c>
-      <x:c r="C12" s="46" t="n">
-        <x:v>91386286.47267893</x:v>
-      </x:c>
-      <x:c r="D12" s="46" t="str">
+      <x:c r="C12" s="24" t="n">
+        <x:v>87435123.8002821</x:v>
+      </x:c>
+      <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
-      <x:c r="A13" s="46" t="str">
-        <x:v>HS_081</x:v>
-      </x:c>
-      <x:c r="B13" s="46" t="str">
+      <x:c r="A13" s="24" t="str">
+        <x:v>HS_081</x:v>
+      </x:c>
+      <x:c r="B13" s="24" t="str">
         <x:v>functional_ppr</x:v>
       </x:c>
-      <x:c r="C13" s="46" t="n">
-        <x:v>91386286.47267893</x:v>
-      </x:c>
-      <x:c r="D13" s="46" t="str">
+      <x:c r="C13" s="24" t="n">
+        <x:v>86872298.1778867</x:v>
+      </x:c>
+      <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
-      <x:c r="A14" s="46" t="str">
-        <x:v>HS_081</x:v>
-      </x:c>
-      <x:c r="B14" s="46" t="str">
+      <x:c r="A14" s="24" t="str">
+        <x:v>HS_081</x:v>
+      </x:c>
+      <x:c r="B14" s="24" t="str">
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
-      <x:c r="C14" s="46" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D14" s="46" t="str">
+      <x:c r="C14" s="24" t="n">
+        <x:v>-3951162.6723968238</x:v>
+      </x:c>
+      <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
-      <x:c r="A15" s="46" t="str">
-        <x:v>HS_081</x:v>
-      </x:c>
-      <x:c r="B15" s="46" t="str">
+      <x:c r="A15" s="24" t="str">
+        <x:v>HS_081</x:v>
+      </x:c>
+      <x:c r="B15" s="24" t="str">
         <x:v>functional_ppr_difference</x:v>
       </x:c>
-      <x:c r="C15" s="46" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D15" s="46" t="str">
+      <x:c r="C15" s="24" t="n">
+        <x:v>-4513988.294792235</x:v>
+      </x:c>
+      <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
-      <x:c r="A16" s="46" t="str">
-        <x:v>HS_081</x:v>
-      </x:c>
-      <x:c r="B16" s="46" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="46" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="D16" s="46" t="str">
+      <x:c r="A16" s="24" t="str">
+        <x:v>HS_081</x:v>
+      </x:c>
+      <x:c r="B16" s="24" t="str">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D16" s="24" t="str">
         <x:v>boolean</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
-      <x:c r="A17" s="46" t="str">
-        <x:v>HS_081</x:v>
-      </x:c>
-      <x:c r="B17" s="46" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="46" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="D17" s="46" t="str">
+      <x:c r="A17" s="24" t="str">
+        <x:v>HS_081</x:v>
+      </x:c>
+      <x:c r="B17" s="24" t="str">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="46" t="str">
-        <x:v>HS_081</x:v>
-      </x:c>
-      <x:c r="B18" s="46" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="46" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="46" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="46" t="str">
-        <x:v>HS_081</x:v>
-      </x:c>
-      <x:c r="B19" s="46" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="46" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="46" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14a8f03961c24001"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R275b7c35680f4e07"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3630,152 +3049,152 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str">
+      <x:c r="A1" s="3" t="str">
         <x:v>HS_081 - Pacific, Southwest</x:v>
       </x:c>
-      <x:c r="B1" s="4"/>
-      <x:c r="C1" s="4"/>
+      <x:c r="B1" s="3"/>
+      <x:c r="C1" s="3"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="12" t="str">
+      <x:c r="A3" s="7" t="str">
         <x:v>Field</x:v>
       </x:c>
-      <x:c r="B3" s="13" t="str">
+      <x:c r="B3" s="8" t="str">
         <x:v>Value</x:v>
       </x:c>
-      <x:c r="C3" s="14" t="str">
+      <x:c r="C3" s="9" t="str">
         <x:v>Notes / source</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="42" t="str">
+      <x:c r="A4" s="22" t="str">
         <x:v>Unit ID</x:v>
       </x:c>
-      <x:c r="B4" s="31" t="str">
-        <x:v>HS_081</x:v>
-      </x:c>
-      <x:c r="C4" s="32" t="str">
+      <x:c r="B4" s="17" t="str">
+        <x:v>HS_081</x:v>
+      </x:c>
+      <x:c r="C4" s="18" t="str">
         <x:v>Sea Around Us region identifier</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="42" t="str">
+      <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="68" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="C5" s="32" t="str">
+      <x:c r="C5" s="18" t="str">
         <x:v>Used by every SPPR formula</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="42" t="str">
+      <x:c r="A6" s="22" t="str">
         <x:v>Year</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="n">
+      <x:c r="B6" s="17" t="n">
         <x:v>2019</x:v>
       </x:c>
-      <x:c r="C6" s="32" t="str">
+      <x:c r="C6" s="18" t="str">
         <x:v>Latest year common to all 84 datasets</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="42" t="str">
+      <x:c r="A7" s="22" t="str">
         <x:v>Region type</x:v>
       </x:c>
-      <x:c r="B7" s="31" t="str">
+      <x:c r="B7" s="17" t="str">
         <x:v>High Seas</x:v>
       </x:c>
-      <x:c r="C7" s="32" t="str">
+      <x:c r="C7" s="18" t="str">
         <x:v>Sea Around Us spatial classification</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="42" t="str">
+      <x:c r="A8" s="22" t="str">
         <x:v>Catch scope</x:v>
       </x:c>
-      <x:c r="B8" s="31" t="str">
+      <x:c r="B8" s="17" t="str">
         <x:v>Landings + Discards</x:v>
       </x:c>
-      <x:c r="C8" s="32" t="str">
+      <x:c r="C8" s="18" t="str">
         <x:v>Reported + unreported; all sectors, gears, entities, and end uses</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="42" t="str">
+      <x:c r="A9" s="22" t="str">
         <x:v>SPPR formula</x:v>
       </x:c>
-      <x:c r="B9" s="31" t="str">
+      <x:c r="B9" s="17" t="str">
         <x:v>(1 / TE)^(TL - 1)</x:v>
       </x:c>
-      <x:c r="C9" s="32" t="str">
+      <x:c r="C9" s="18" t="str">
         <x:v>TE is the Metadata!B5 value</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="42" t="str">
+      <x:c r="A10" s="22" t="str">
         <x:v>PPR formula</x:v>
       </x:c>
-      <x:c r="B10" s="31" t="str">
+      <x:c r="B10" s="17" t="str">
         <x:v>Catch tonnes × SPPR</x:v>
       </x:c>
-      <x:c r="C10" s="32" t="str">
+      <x:c r="C10" s="18" t="str">
         <x:v>Unit: tonnes primary-production equivalent</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="42" t="str">
+      <x:c r="A11" s="22" t="str">
         <x:v>Wet-weight/carbon divisor</x:v>
       </x:c>
-      <x:c r="B11" s="31" t="str">
+      <x:c r="B11" s="17" t="str">
         <x:v>Not applied</x:v>
       </x:c>
-      <x:c r="C11" s="32" t="str">
+      <x:c r="C11" s="18" t="str">
         <x:v>The paper's /9 conversion is intentionally omitted</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="42" t="str">
+      <x:c r="A12" s="22" t="str">
         <x:v>Primary TL source</x:v>
       </x:c>
-      <x:c r="B12" s="31" t="str">
+      <x:c r="B12" s="17" t="str">
         <x:v>2020 supplement MeanTL</x:v>
       </x:c>
-      <x:c r="C12" s="32" t="str">
+      <x:c r="C12" s="18" t="str">
         <x:v>No SPPR regression from the supplement is used</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="42" t="str">
+      <x:c r="A13" s="22" t="str">
         <x:v>Secondary TL source</x:v>
       </x:c>
-      <x:c r="B13" s="31" t="str">
+      <x:c r="B13" s="17" t="str">
         <x:v>Sea Around Us exploited organisms</x:v>
       </x:c>
-      <x:c r="C13" s="32" t="str">
+      <x:c r="C13" s="18" t="str">
         <x:v>Exact taxon matches, followed by documented fallbacks</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="42" t="str">
+      <x:c r="A14" s="22" t="str">
         <x:v>Catch data URL</x:v>
       </x:c>
-      <x:c r="B14" s="31" t="str">
+      <x:c r="B14" s="17" t="str">
         <x:v>https://www.seaaroundus.org/data/</x:v>
       </x:c>
-      <x:c r="C14" s="32" t="str">
+      <x:c r="C14" s="18" t="str">
         <x:v>Frozen archive: raw_data/SAU_downloads/HS_081-catch.zip</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="43" t="str">
+      <x:c r="A15" s="23" t="str">
         <x:v>Method source</x:v>
       </x:c>
-      <x:c r="B15" s="34" t="str">
+      <x:c r="B15" s="20" t="str">
         <x:v>Pauly &amp; Christensen (1995)</x:v>
       </x:c>
-      <x:c r="C15" s="35" t="str">
+      <x:c r="C15" s="21" t="str">
         <x:v>Nature 374:255-257</x:v>
       </x:c>
     </x:row>
